--- a/Combined Justification 8.05.2026.xlsx
+++ b/Combined Justification 8.05.2026.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="897" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="897" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sum of Primary Studies " sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Analysis Justification" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Approach" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baskets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="default conditions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qualtrics" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bakery  " sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dairy Eggs Fridge" sheetId="7" state="visible" r:id="rId7"/>
@@ -21,16 +21,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pantry" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ready to eat " sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vegetables" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baskets" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,12 +116,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="PplxSans"/>
       <charset val="1"/>
       <b val="1"/>
@@ -128,23 +123,27 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -213,22 +212,28 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
+        <fgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF77474"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -286,23 +291,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -385,10 +391,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -409,37 +415,107 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -8617,6 +8693,6365 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G241"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Healthy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unhealthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coles Bakery Apple Crown Danish | 2 pack</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Coles Bagels Plain 4 Pack | 360g</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Coles BBQ Cheese And Bacon Pizza Roll | 2 pack</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Coles All Butter Croissants 4 Pack | 168g</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Coles Cheese &amp; Bacon Rolls | 4 pack</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Coles Choc Chip Hot Cross Bun | 6 Pack</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Coles Bakery Cinnamon Scrolls | 2 Pack</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Coles Double Choc Muffins 9 Pack | 315g</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Coles Lemon &amp; Raspberry Flavoured Tarts 6 Pack | 270g</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Woolworths Ham &amp; Cheese Croissant 2 pack</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Coles High Fibre White Sandwich Bread | 700g</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Coles Bakery Jam Filled Berliner Donut | 2 pack</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Coles Bread High Fibre Multigrain | 700g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Abbott's Bakery Dark Rye | 700g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Simson's Pantry Preservative Free Mixed Wholegrain Large Wraps 8 Pack | 528g</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Coles High Fibre Wholemeal Bread | 700g</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tip Top Muffins English Wholemeal | 400g</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tip Top Gourmet Pizza Base Wholemeal 2 Pack | 440g</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coles Wholemeal Rolls | 6 pack</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DEF1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pauls Low Fat Less Sugar Vanilla Custard | 600g</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DEF2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Coles Lite Reduced Fat Milk | 2L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DEF3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Coles Light Ricotta 375g</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DEF4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Coles Regular Soy Milk | 1L</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DEF5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Farmers Union Protein Yoghurt 900g</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DEF6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Coles Free Range Eggs 12 Pack | 700g</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DEF7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bulla Cottage Cheese Original 200g</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DEF8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tempo Reduced Fat Cheddar Cheese Block  250g</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DEF9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>On The Menu Fresh Napoli Sauce | 425g</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DEF10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Simply Better Plain Firm Tofu | 375g</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEF11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Primo Champagne Leg Ham | 100g</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DEF12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cocobella Dairy Free Natural Coconut Yoghurt | 500g</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEF13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Primo Mild Hungarian Salami | 80g</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEF14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Primo Roast Pastrami Thinly Sliced | 80g</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEF15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Primo Chicken Breast Thinly Sliced | 80g</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DEF16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Latina Fresh Creamy Carbonara Pasta Sauce | 425g</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DEF17</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Primo Middle Bacon | 750g</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DEF18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Primo Silverside | 80g</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DEF19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>The Yoghurt Shop Belgian Triple Chocolate | 170g</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DEF20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Primo Maple Streaky Bacon | 175g</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DEF21</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Moira Macs RSPCA Approved Shredded Chicken | 420g</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DEF22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Don Traditional Kabana | 200g</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DEF23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Primo Reserve Prosciutto Sliced Deli Meat | 100g</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DEF24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Primo Sliced Turkey Breast | 80g</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DEF25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Wicked Sister High Protein Chocolate Pudding | 170g</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DEF26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Casalingo Sliced Pancetta | 100g</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DEF27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>K R Castlemaine Fritz Smiley Loaf From The Deli per 100g</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DEF28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Dairy Eggs Fridge</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Primo Short Cut Bacon | 200g</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DRK1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Spring Water</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DRK2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sparkling Water</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DRK3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Soda water</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DRK4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Orange Juice No added Sugar</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DRK5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tropical punch juice</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DRK6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chocolate flavoured coconut water</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DRK7</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sports Drink Flavoured</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DRK8</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Flavoured water wildberry</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DRK9</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Energy Drink</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DRK10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>High protein chocolate shake</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DRK11</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Protein Water Berry Whey Protein Isolate</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DRK12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Cola flavoured soda</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DRK13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Protein water citrus</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SNA1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Multigrain crackers and light cheese</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SNA2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wholegrain rice crackers</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SNA3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Multigrain crispbread crackers</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SNA4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mini rice crisps milk chocolate</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SNA5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Mix lollies</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SNA6</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jelly</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SNA7</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jelly beans</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SNA8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Liquorice</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SNA9</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Marshmallows</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SNA10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Milk chocolate</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SNA11</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Hazelnut spread</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SNA12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mayple syrup</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SNA13</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Snake lollies</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SNA14</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Plain crackers</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SNA15</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Pretzels</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SNA16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Original potato chips</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SNA17</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>chicken potato chips</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SNA18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salt &amp; Vinegar chips</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SNA19</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Cheese corn chips</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SNA20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Choclate chip cookies</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SNA21</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Biscuits shortbread creams</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SNA22</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chocolate coated biscuits</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SNA23</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chocolate cream wafers</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SNA24</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nut bars chocolate peanut &amp; almond</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SNA25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Rice bubbles snack bars</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SNA26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Flavoured rainbow Sticks</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SNA27</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Crunchy oats &amp; honey bars</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SNA28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chocolate oat slices</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FRU1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nectarine</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FRU2</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Grapes</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FRU3</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FRU4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Strawberries</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FRU5</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>blueberries</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FRU6</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>pears</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FRU7</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>pineapple</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FRU8</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FRU9</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bannanas</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FRU10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oranges</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FRU11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Kiwi fruit</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FRU12</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Canned peaches</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FRU13</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Canned fruit salad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FRU14</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Dried apple</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FRU15</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Dried mango</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FRU16</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Banana Chips</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FRU17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Freeze dried fruit dipped in chocolate</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FRU18</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fruit Jelly Cup</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FRU19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fruit string</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FRU20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Fruit</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Fruit roll up</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MEA1</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Extra lean beef mince</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MEA2</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Beef sizzle steak</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MEA3</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Lamb leg diced</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MEA4</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Pork sizzle steaks</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MEA5</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Extra lean pork mince</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MEA6</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Kangaroo diced</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MEA7</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chicken breast fillets</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MEA8</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Turkey mince</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MEA9</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Basa</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MEA10</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MEA11</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Barramundi</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MEA12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tuna steaks</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MEA13</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Thin Bbq sausages</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MEA14</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Beef sausages</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MEA15</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Beef burgers patties</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MEA16</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Lamb burgers</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MEA17</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Beef Bbq burgers</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MEA18</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Kransky bites</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MEA19</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Beef brisket burgers</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MEA20</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Beef chevap</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MEA21</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Deli continental chorizo</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MEA22</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Meat Seafood</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Roll chicken</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FRZ1</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Frozen mixed berries</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FRZ2</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Frozen mango</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FRZ3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Frozen strawberries</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FRZ4</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Frozen Broccoli</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FRZ5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Frozen Vegetable Mix</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FRZ6</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Frozen Cauliflower</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FRZ7</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Frozen Peas</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FRZ8</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Frozen Beans</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FRZ9</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chinese Stir Fry Mix Veg</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FRZ10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Frozen Carrots</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FRZ11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Flavoured Iceblocks</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FRZ12</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Frozen Dessert Cones - Brownie</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FRZ13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>French Cream Cheesecake</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FRZ14</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Tiramisu</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>FRZ15</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Apple pie</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FRZ16</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chocolate Bavarian</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FRZ17</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Strawberry cheesecake</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FRZ18</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Chocolate cake</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>FRZ19</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Meatlovers Pizza</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>FRZ20</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Icecream cake</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>FRZ21</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Connoisseur Camarosa Strawberry Gourmet Ice Cream 1L</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FRZ22</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Connoisseur Ice Cream Classic Vanilla Tub 1L</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>FRZ23</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Cheese &amp; Bacon Pizza</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FRZ24</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hawaiin Pizza</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FRZ25</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Puff Pastry Sheets</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FRZ26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Shortcrust Pastry</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FRZ27</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Beef Curry Puff</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FRZ28</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Quiche Cheese &amp; Bacon</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FRZ29</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Dim Sim</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PAN1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Bolognese sauce</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PAN2</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Butter chicken sauce</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PAN3</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Sweet and sour stir fry sauce</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PAN4</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Rogan josh sauce</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PAN5</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tikka masala sauce</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PAN6</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tortillas</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PAN7</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PAN8</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Long grain rice</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PAN9</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Pasta spaghetti</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PAN10</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Pasta penne</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PAN11</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Glass noodles</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PAN12</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Cous cous</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PAN13</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tri colour quinoa</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PAN14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Kidney beans</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PAN15</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Chick peas</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PAN16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Black beans</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PAN17</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Baked beans</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PAN18</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Red split lentils</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PAN19</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Whole green lentils</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PAN20</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Lentil soup mix dried</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PAN21</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Springwater tuna</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PAN22</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sprinwater salmon</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PAN23</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Unsalted mixed nuts</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PAN24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Unsalted cashews</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PAN25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Organic peanut butter</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PAN26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Beetroot</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PAN27</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Corn Kernels no added salt canned</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PAN28</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Organic tomatoes canned</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PAN29</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Pumpkin seeds</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PAN30</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Black chia seeds</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PAN31</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Sunflower seeds</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PAN32</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Walnuts</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PAN33</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Almonds</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PAN34</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Korma simmer sauce</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PAN35</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Vindaloo simmer sauce</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PAN36</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Honey soy stir fry sauce</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PAN37</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Pappadams</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PAN38</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Chocolate flavoured cereal</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PAN39</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Rainbow flavoured cereal</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PAN40</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Chocolate coated peanuts</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PAN41</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Choc coated almonds</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PAN42</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Beef jerky</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PAN43</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Chicken flavoured noodle cup</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PAN44</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ramen noodle cup mild</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>RTE1</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Lentil salad with olive oil</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>RTE2</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Green salad bowl</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>RTE3</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Chicken &amp; corn soup</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>RTE4</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Chicken noodle soup</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>RTE5</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Tomato &amp; basil soup</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>RTE6</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Broccoli, cauliflower &amp; parmesan soup</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>RTE7</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Pea &amp; ham soup</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>RTE8</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Minestrone soup</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>RTE9</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Ultra green soup</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>RTE10</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Butter chicken with rice</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>RTE11</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Beef stroganoff with rice</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>RTE12</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Macaroni cheese</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>RTE13</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Chicken &amp; bacon pasta bake</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>RTE14</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Protein BBQ chicken burrito</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>RTE15</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Pulled pork smokey chipolte burrito</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>RTE16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Easy enchilada</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>RTE17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Pastie</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>RTE18</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Beef cheese &amp; bacon pie</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>RTE19</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Microwaveable sausage Roll</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>RTE20</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Ready to eat</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Samosa</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>unhealthy</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>VEG1</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Broccoli</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>VEG2</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Carrots</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>VEG3</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Zucchini</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>VEG4</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>tomatoes</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>VEG5</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Capsicum</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>VEG6</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>VEG7</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Lettuce</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>VEG8</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Potatoe</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>VEG9</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Cauliflower</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>VEG10</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Brown onion</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>VEG11</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Pumpkin</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>VEG12</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sweet corn</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>VEG13</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Asian choy pak</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>VEG14</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Green beans</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>VEG15</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Eggplant</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>VEG16</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Celery</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>VEG17</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Sweet potatoe</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet3">
@@ -8952,17 +15387,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
+    <row r="1" ht="50.1" customHeight="1">
       <c r="A1" s="46" t="inlineStr">
         <is>
           <t>Dimension</t>
@@ -9039,13 +15468,13 @@
 (items available)</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr"/>
-      <c r="C3" s="52" t="inlineStr"/>
-      <c r="D3" s="52" t="inlineStr"/>
-      <c r="E3" s="52" t="inlineStr"/>
-      <c r="F3" s="52" t="inlineStr"/>
-      <c r="G3" s="52" t="inlineStr"/>
-      <c r="H3" s="52" t="inlineStr"/>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
       <c r="I3" s="53" t="inlineStr">
         <is>
           <t>240 items
@@ -9060,7 +15489,7 @@
 (typical selection)</t>
         </is>
       </c>
-      <c r="B4" s="54" t="inlineStr"/>
+      <c r="B4" s="54" t="n"/>
       <c r="C4" s="54" t="inlineStr">
         <is>
           <t>30 (with qty)
@@ -9073,10 +15502,10 @@
 ~25 (with qty)</t>
         </is>
       </c>
-      <c r="E4" s="54" t="inlineStr"/>
-      <c r="F4" s="54" t="inlineStr"/>
-      <c r="G4" s="54" t="inlineStr"/>
-      <c r="H4" s="54" t="inlineStr"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
       <c r="I4" s="53" t="inlineStr">
         <is>
           <t>Up to 30
@@ -9091,7 +15520,7 @@
 (can select &gt;1 of same item)</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr"/>
+      <c r="B5" s="52" t="n"/>
       <c r="C5" s="52" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9102,10 +15531,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr"/>
-      <c r="F5" s="52" t="inlineStr"/>
-      <c r="G5" s="52" t="inlineStr"/>
-      <c r="H5" s="52" t="inlineStr"/>
+      <c r="E5" s="52" t="n"/>
+      <c r="F5" s="52" t="n"/>
+      <c r="G5" s="52" t="n"/>
+      <c r="H5" s="52" t="n"/>
       <c r="I5" s="53" t="inlineStr">
         <is>
           <t>No
@@ -9120,13 +15549,13 @@
 (hard cap on selections)</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr"/>
-      <c r="C6" s="54" t="inlineStr"/>
-      <c r="D6" s="54" t="inlineStr"/>
-      <c r="E6" s="54" t="inlineStr"/>
-      <c r="F6" s="54" t="inlineStr"/>
-      <c r="G6" s="54" t="inlineStr"/>
-      <c r="H6" s="54" t="inlineStr"/>
+      <c r="B6" s="54" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="54" t="n"/>
+      <c r="E6" s="54" t="n"/>
+      <c r="F6" s="54" t="n"/>
+      <c r="G6" s="54" t="n"/>
+      <c r="H6" s="54" t="n"/>
       <c r="I6" s="53" t="inlineStr">
         <is>
           <t>30 items</t>
@@ -9171,8 +15600,8 @@
 SNAP allowance)</t>
         </is>
       </c>
-      <c r="E8" s="54" t="inlineStr"/>
-      <c r="F8" s="54" t="inlineStr"/>
+      <c r="E8" s="54" t="n"/>
+      <c r="F8" s="54" t="n"/>
       <c r="G8" s="54" t="inlineStr">
         <is>
           <t>$25/child/month
@@ -9181,7 +15610,7 @@
 breastfeeding)</t>
         </is>
       </c>
-      <c r="H8" s="54" t="inlineStr"/>
+      <c r="H8" s="54" t="n"/>
       <c r="I8" s="53" t="inlineStr">
         <is>
           <t>No budget constraint</t>
@@ -9194,21 +15623,21 @@
           <t>Benefit programme</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr"/>
-      <c r="C9" s="52" t="inlineStr"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
       <c r="D9" s="52" t="inlineStr">
         <is>
           <t>SNAP</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr"/>
-      <c r="F9" s="52" t="inlineStr"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
       <c r="G9" s="52" t="inlineStr">
         <is>
           <t>WIC</t>
         </is>
       </c>
-      <c r="H9" s="52" t="inlineStr"/>
+      <c r="H9" s="52" t="n"/>
       <c r="I9" s="53" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -9242,9 +15671,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr"/>
-      <c r="D11" s="52" t="inlineStr"/>
-      <c r="E11" s="52" t="inlineStr"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
       <c r="F11" s="52" t="inlineStr">
         <is>
           <t>Yes
@@ -9256,7 +15685,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="52" t="inlineStr"/>
+      <c r="H11" s="52" t="n"/>
       <c r="I11" s="53" t="inlineStr">
         <is>
           <t>Yes
@@ -9275,9 +15704,9 @@
           <t>None</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr"/>
-      <c r="D12" s="54" t="inlineStr"/>
-      <c r="E12" s="54" t="inlineStr"/>
+      <c r="C12" s="54" t="n"/>
+      <c r="D12" s="54" t="n"/>
+      <c r="E12" s="54" t="n"/>
       <c r="F12" s="54" t="inlineStr">
         <is>
           <t>5 fruit items</t>
@@ -9288,7 +15717,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="H12" s="54" t="inlineStr"/>
+      <c r="H12" s="54" t="n"/>
       <c r="I12" s="53" t="inlineStr">
         <is>
           <t>2 items per category
@@ -9303,13 +15732,13 @@
 (# of distinct default carts)</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr"/>
-      <c r="C13" s="52" t="inlineStr"/>
-      <c r="D13" s="52" t="inlineStr"/>
-      <c r="E13" s="52" t="inlineStr"/>
-      <c r="F13" s="52" t="inlineStr"/>
-      <c r="G13" s="52" t="inlineStr"/>
-      <c r="H13" s="52" t="inlineStr"/>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
       <c r="I13" s="53" t="inlineStr">
         <is>
           <t>4 conditions:
@@ -9339,15 +15768,15 @@
           <t>Sessions / time points</t>
         </is>
       </c>
-      <c r="B15" s="52" t="inlineStr"/>
-      <c r="C15" s="52" t="inlineStr"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
       <c r="D15" s="52" t="inlineStr">
         <is>
           <t>5 time points</t>
         </is>
       </c>
-      <c r="E15" s="52" t="inlineStr"/>
-      <c r="F15" s="52" t="inlineStr"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
       <c r="G15" s="52" t="inlineStr">
         <is>
           <t>Items to last
@@ -9393,8 +15822,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C17" s="52" t="inlineStr"/>
-      <c r="D17" s="52" t="inlineStr"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
       <c r="E17" s="52" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9427,9 +15856,9 @@
           <t>Recipes per week</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr"/>
-      <c r="C18" s="54" t="inlineStr"/>
-      <c r="D18" s="54" t="inlineStr"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
       <c r="E18" s="54" t="inlineStr">
         <is>
           <t>3</t>
@@ -9440,13 +15869,13 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G18" s="54" t="inlineStr"/>
+      <c r="G18" s="54" t="n"/>
       <c r="H18" s="54" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I18" s="53" t="inlineStr"/>
+      <c r="I18" s="53" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="51" t="inlineStr">
@@ -9455,16 +15884,16 @@
 per recipe</t>
         </is>
       </c>
-      <c r="B19" s="52" t="inlineStr"/>
-      <c r="C19" s="52" t="inlineStr"/>
-      <c r="D19" s="52" t="inlineStr"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
       <c r="E19" s="52" t="inlineStr">
         <is>
           <t>~10.2
 (163 total ÷ 16 recipes)</t>
         </is>
       </c>
-      <c r="F19" s="52" t="inlineStr"/>
+      <c r="F19" s="52" t="n"/>
       <c r="G19" s="52" t="inlineStr">
         <is>
           <t>~10
@@ -9477,7 +15906,7 @@
 (12 + 8 + 9 ÷ 3)</t>
         </is>
       </c>
-      <c r="I19" s="53" t="inlineStr"/>
+      <c r="I19" s="53" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="51" t="inlineStr">
@@ -9486,15 +15915,15 @@
 per week</t>
         </is>
       </c>
-      <c r="B20" s="54" t="inlineStr"/>
-      <c r="C20" s="54" t="inlineStr"/>
-      <c r="D20" s="54" t="inlineStr"/>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
       <c r="E20" s="54" t="inlineStr">
         <is>
           <t>~30.6</t>
         </is>
       </c>
-      <c r="F20" s="54" t="inlineStr"/>
+      <c r="F20" s="54" t="n"/>
       <c r="G20" s="54" t="inlineStr">
         <is>
           <t>~30</t>
@@ -9506,7 +15935,7 @@
 (+ fruit &amp; veg serving)</t>
         </is>
       </c>
-      <c r="I20" s="53" t="inlineStr"/>
+      <c r="I20" s="53" t="n"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="51" t="inlineStr">
@@ -9514,9 +15943,9 @@
           <t>Recipe notes</t>
         </is>
       </c>
-      <c r="B21" s="52" t="inlineStr"/>
-      <c r="C21" s="52" t="inlineStr"/>
-      <c r="D21" s="52" t="inlineStr"/>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
       <c r="E21" s="52" t="inlineStr">
         <is>
           <t>16 recipe options in
@@ -9530,7 +15959,7 @@
 sample cart fruit-only</t>
         </is>
       </c>
-      <c r="G21" s="52" t="inlineStr"/>
+      <c r="G21" s="52" t="n"/>
       <c r="H21" s="52" t="inlineStr">
         <is>
           <t>Recipe 1: 12 ingredients
@@ -9539,7 +15968,7 @@
 +fruit/veg serving</t>
         </is>
       </c>
-      <c r="I21" s="53" t="inlineStr"/>
+      <c r="I21" s="53" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="48" t="inlineStr">
@@ -9562,13 +15991,13 @@
           <t>Classification method</t>
         </is>
       </c>
-      <c r="B23" s="52" t="inlineStr"/>
-      <c r="C23" s="52" t="inlineStr"/>
-      <c r="D23" s="52" t="inlineStr"/>
-      <c r="E23" s="52" t="inlineStr"/>
-      <c r="F23" s="52" t="inlineStr"/>
-      <c r="G23" s="52" t="inlineStr"/>
-      <c r="H23" s="52" t="inlineStr"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
       <c r="I23" s="53" t="inlineStr">
         <is>
           <t>Binary per item:
@@ -9582,13 +16011,13 @@
           <t>Health outcome measure</t>
         </is>
       </c>
-      <c r="B24" s="54" t="inlineStr"/>
-      <c r="C24" s="54" t="inlineStr"/>
-      <c r="D24" s="54" t="inlineStr"/>
-      <c r="E24" s="54" t="inlineStr"/>
-      <c r="F24" s="54" t="inlineStr"/>
-      <c r="G24" s="54" t="inlineStr"/>
-      <c r="H24" s="54" t="inlineStr"/>
+      <c r="B24" s="54" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
       <c r="I24" s="53" t="inlineStr">
         <is>
           <t>Health score =
@@ -9604,1003 +16033,674 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet5">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="16" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="32.28515625" customWidth="1" min="3" max="3"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12.140625" customWidth="1" min="6" max="6"/>
-    <col width="18.28515625" customWidth="1" min="7" max="7"/>
-    <col width="16.140625" customWidth="1" min="8" max="8"/>
+    <col width="19.85546875" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16.7109375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="19.42578125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="20" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customFormat="1" customHeight="1" s="38" thickBot="1">
-      <c r="A1" s="36" t="inlineStr">
-        <is>
-          <t>Item ID</t>
-        </is>
-      </c>
-      <c r="B1" s="36" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" s="36" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="D1" s="36" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="E1" s="37" t="inlineStr">
-        <is>
-          <t>HealthyA</t>
-        </is>
-      </c>
-      <c r="F1" s="37" t="inlineStr">
-        <is>
-          <t>HealthyB</t>
-        </is>
-      </c>
-      <c r="G1" s="37" t="inlineStr">
-        <is>
-          <t>UnHealthyA</t>
-        </is>
-      </c>
-      <c r="H1" s="37" t="inlineStr">
-        <is>
-          <t>UnHealthyB</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A2" s="35">
-        <f>'Bakery  '!A2</f>
-        <v/>
-      </c>
-      <c r="B2" s="35">
-        <f>'Bakery  '!B2</f>
-        <v/>
-      </c>
-      <c r="C2" s="35">
-        <f>'Bakery  '!D2</f>
-        <v/>
-      </c>
-      <c r="D2" s="35">
-        <f>'Bakery  '!E2</f>
-        <v/>
-      </c>
-      <c r="E2" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A3" s="35">
-        <f>'Bakery  '!A3</f>
-        <v/>
-      </c>
-      <c r="B3" s="35">
-        <f>'Bakery  '!B3</f>
-        <v/>
-      </c>
-      <c r="C3" s="35">
-        <f>'Bakery  '!D3</f>
-        <v/>
-      </c>
-      <c r="D3" s="35">
-        <f>'Bakery  '!E3</f>
-        <v/>
-      </c>
-      <c r="E3" s="35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="35">
-        <f>'Bakery  '!A4</f>
-        <v/>
-      </c>
-      <c r="B4" s="35">
-        <f>'Bakery  '!B4</f>
-        <v/>
-      </c>
-      <c r="C4" s="35">
-        <f>'Bakery  '!D4</f>
-        <v/>
-      </c>
-      <c r="D4" s="35">
-        <f>'Bakery  '!E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A5" s="35">
-        <f>'Bakery  '!A5</f>
-        <v/>
-      </c>
-      <c r="B5" s="35">
-        <f>'Bakery  '!B5</f>
-        <v/>
-      </c>
-      <c r="C5" s="35">
-        <f>'Bakery  '!D5</f>
-        <v/>
-      </c>
-      <c r="D5" s="35">
-        <f>'Bakery  '!E5</f>
-        <v/>
-      </c>
-      <c r="E5" s="35" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A6" s="35">
-        <f>'Bakery  '!A6</f>
-        <v/>
-      </c>
-      <c r="B6" s="35">
-        <f>'Bakery  '!B6</f>
-        <v/>
-      </c>
-      <c r="C6" s="35">
-        <f>'Bakery  '!D6</f>
-        <v/>
-      </c>
-      <c r="D6" s="35">
-        <f>'Bakery  '!E6</f>
-        <v/>
-      </c>
-      <c r="E6" s="35" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A7" s="35">
-        <f>'Bakery  '!A7</f>
-        <v/>
-      </c>
-      <c r="B7" s="35">
-        <f>'Bakery  '!B7</f>
-        <v/>
-      </c>
-      <c r="C7" s="35">
-        <f>'Bakery  '!D7</f>
-        <v/>
-      </c>
-      <c r="D7" s="35">
-        <f>'Bakery  '!E7</f>
-        <v/>
-      </c>
-      <c r="E7" s="35" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="35">
-        <f>'Bakery  '!A8</f>
-        <v/>
-      </c>
-      <c r="B8" s="35">
-        <f>'Bakery  '!B8</f>
-        <v/>
-      </c>
-      <c r="C8" s="35">
-        <f>'Bakery  '!D8</f>
-        <v/>
-      </c>
-      <c r="D8" s="35">
-        <f>'Bakery  '!E8</f>
-        <v/>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A9" s="35">
-        <f>'Bakery  '!A9</f>
-        <v/>
-      </c>
-      <c r="B9" s="35">
-        <f>'Bakery  '!B9</f>
-        <v/>
-      </c>
-      <c r="C9" s="35">
-        <f>'Bakery  '!D9</f>
-        <v/>
-      </c>
-      <c r="D9" s="35">
-        <f>'Bakery  '!E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A10" s="35">
-        <f>'Bakery  '!A10</f>
-        <v/>
-      </c>
-      <c r="B10" s="35">
-        <f>'Bakery  '!B10</f>
-        <v/>
-      </c>
-      <c r="C10" s="35">
-        <f>'Bakery  '!D10</f>
-        <v/>
-      </c>
-      <c r="D10" s="35">
-        <f>'Bakery  '!E10</f>
-        <v/>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A11" s="35">
-        <f>'Bakery  '!A11</f>
-        <v/>
-      </c>
-      <c r="B11" s="35">
-        <f>'Bakery  '!B11</f>
-        <v/>
-      </c>
-      <c r="C11" s="35">
-        <f>'Bakery  '!D11</f>
-        <v/>
-      </c>
-      <c r="D11" s="35">
-        <f>'Bakery  '!E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A12" s="35">
-        <f>'Bakery  '!A12</f>
-        <v/>
-      </c>
-      <c r="B12" s="35">
-        <f>'Bakery  '!B12</f>
-        <v/>
-      </c>
-      <c r="C12" s="35">
-        <f>'Bakery  '!D12</f>
-        <v/>
-      </c>
-      <c r="D12" s="35">
-        <f>'Bakery  '!E12</f>
-        <v/>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A13" s="35">
-        <f>'Bakery  '!A13</f>
-        <v/>
-      </c>
-      <c r="B13" s="35">
-        <f>'Bakery  '!B13</f>
-        <v/>
-      </c>
-      <c r="C13" s="35">
-        <f>'Bakery  '!D13</f>
-        <v/>
-      </c>
-      <c r="D13" s="35">
-        <f>'Bakery  '!E13</f>
-        <v/>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A14" s="35">
-        <f>'Bakery  '!A14</f>
-        <v/>
-      </c>
-      <c r="B14" s="35">
-        <f>'Bakery  '!B14</f>
-        <v/>
-      </c>
-      <c r="C14" s="35">
-        <f>'Bakery  '!D14</f>
-        <v/>
-      </c>
-      <c r="D14" s="35">
-        <f>'Bakery  '!E14</f>
-        <v/>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A15" s="35">
-        <f>'Bakery  '!A15</f>
-        <v/>
-      </c>
-      <c r="B15" s="35">
-        <f>'Bakery  '!B15</f>
-        <v/>
-      </c>
-      <c r="C15" s="35">
-        <f>'Bakery  '!D15</f>
-        <v/>
-      </c>
-      <c r="D15" s="35">
-        <f>'Bakery  '!E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A16" s="35">
-        <f>'Bakery  '!A16</f>
-        <v/>
-      </c>
-      <c r="B16" s="35">
-        <f>'Bakery  '!B16</f>
-        <v/>
-      </c>
-      <c r="C16" s="35">
-        <f>'Bakery  '!D16</f>
-        <v/>
-      </c>
-      <c r="D16" s="35">
-        <f>'Bakery  '!E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A17" s="35">
-        <f>'Bakery  '!A17</f>
-        <v/>
-      </c>
-      <c r="B17" s="35">
-        <f>'Bakery  '!B17</f>
-        <v/>
-      </c>
-      <c r="C17" s="35">
-        <f>'Bakery  '!D17</f>
-        <v/>
-      </c>
-      <c r="D17" s="35">
-        <f>'Bakery  '!E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A18" s="35">
-        <f>'Bakery  '!A18</f>
-        <v/>
-      </c>
-      <c r="B18" s="35">
-        <f>'Bakery  '!B18</f>
-        <v/>
-      </c>
-      <c r="C18" s="35">
-        <f>'Bakery  '!D18</f>
-        <v/>
-      </c>
-      <c r="D18" s="35">
-        <f>'Bakery  '!E18</f>
-        <v/>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="35">
-        <f>'Bakery  '!A19</f>
-        <v/>
-      </c>
-      <c r="B19" s="35">
-        <f>'Bakery  '!B19</f>
-        <v/>
-      </c>
-      <c r="C19" s="35">
-        <f>'Bakery  '!D19</f>
-        <v/>
-      </c>
-      <c r="D19" s="35">
-        <f>'Bakery  '!E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A20" s="35">
-        <f>'Bakery  '!A20</f>
-        <v/>
-      </c>
-      <c r="B20" s="35">
-        <f>'Bakery  '!B20</f>
-        <v/>
-      </c>
-      <c r="C20" s="35">
-        <f>'Bakery  '!D20</f>
-        <v/>
-      </c>
-      <c r="D20" s="35">
-        <f>'Bakery  '!E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="45" t="n"/>
-      <c r="B21" s="45" t="n"/>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="45" t="n"/>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example Coffino 2020 </t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Healthy 80% = 24 Green, 6 red </t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Neutral 50% = 15 green, 15 red</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unhealthy 20% = 6 green, 24 red</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lettuce </t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lettuce </t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lettuce </t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>frozen mix veg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> eggs </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cucumber </t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banannas </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>red onion</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>red onion</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole grain wraps </t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>chicken breast</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whole wheat pita bread </t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Whole Grain wraps</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lean mince meat </t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lean mince meat </t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peanut butter </t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic Peanut butter </t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>chicken breast</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein Greek Yoghurt </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>current jelly</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lean Mince Meat </t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>sweet potatoes</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cinnamon scroll </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drumstick chicken </t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chicken breast </t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bananas </t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>Butter croissant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red potatoes </t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sweet potatoes </t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrots </t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>Double choc muffins</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banannas </t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bananas </t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>canned black beans low sodium</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>Chocolate coated biscuits</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">white mushrooms </t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mushrooms </t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole wheat spagehtti </t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>Mix lollies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrots </t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrots </t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>frozen mix veg</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chocolate Oat Slices </t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>apples</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>apples</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protein greek yoghurt </t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>Chocolate cereal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">canned black beans low sodium </t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">canned black beans low sodium </t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tuna in spring water </t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>Triple Chocolate chip yoghurt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole wheat spaghetti </t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole wheat spaghetti </t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">free range eggs </t>
+        </is>
+      </c>
+      <c r="D16" s="55" t="inlineStr">
+        <is>
+          <t>Original potato chips</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frozen broccoli </t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frozen broccoli </t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cinnamon scroll </t>
+        </is>
+      </c>
+      <c r="D17" s="55" t="inlineStr">
+        <is>
+          <t>Short cut bacon</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>frozen brussel sprouts</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frozen mix veg </t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Double Choc Muffin </t>
+        </is>
+      </c>
+      <c r="D18" s="55" t="inlineStr">
+        <is>
+          <t>Champagne leg ham</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ragu sauce traditional </t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolognase sauce traditional </t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>Apple Crown Danish</t>
+        </is>
+      </c>
+      <c r="D19" s="55" t="inlineStr">
+        <is>
+          <t>Deli continental chorizo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">non fat strawberry yoghurt </t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protein Greek Yoghurt </t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>Short Cut Bacon</t>
+        </is>
+      </c>
+      <c r="D20" s="55" t="inlineStr">
+        <is>
+          <t>Thin BBQ sausages</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tuna in spring water </t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tuna in spring water </t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>Champagne Leg Ham</t>
+        </is>
+      </c>
+      <c r="D21" s="55" t="inlineStr">
+        <is>
+          <t>Beef burger patties</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <f>'Dairy Eggs Fridge'!A2</f>
-        <v/>
-      </c>
-      <c r="B22">
-        <f>'Dairy Eggs Fridge'!B2</f>
-        <v/>
-      </c>
-      <c r="C22">
-        <f>'Dairy Eggs Fridge'!D2</f>
-        <v/>
-      </c>
-      <c r="D22">
-        <f>'Dairy Eggs Fridge'!E2</f>
-        <v/>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <f>'Dairy Eggs Fridge'!A3</f>
-        <v/>
-      </c>
-      <c r="B23">
-        <f>'Dairy Eggs Fridge'!B3</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>'Dairy Eggs Fridge'!D3</f>
-        <v/>
-      </c>
-      <c r="D23">
-        <f>'Dairy Eggs Fridge'!E3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <f>'Dairy Eggs Fridge'!A4</f>
-        <v/>
-      </c>
-      <c r="B24">
-        <f>'Dairy Eggs Fridge'!B4</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>'Dairy Eggs Fridge'!D4</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>'Dairy Eggs Fridge'!E4</f>
-        <v/>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <f>'Dairy Eggs Fridge'!A5</f>
-        <v/>
-      </c>
-      <c r="B25">
-        <f>'Dairy Eggs Fridge'!B5</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>'Dairy Eggs Fridge'!D5</f>
-        <v/>
-      </c>
-      <c r="D25">
-        <f>'Dairy Eggs Fridge'!E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <f>'Dairy Eggs Fridge'!A6</f>
-        <v/>
-      </c>
-      <c r="B26">
-        <f>'Dairy Eggs Fridge'!B6</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>'Dairy Eggs Fridge'!D6</f>
-        <v/>
-      </c>
-      <c r="D26">
-        <f>'Dairy Eggs Fridge'!E6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <f>'Dairy Eggs Fridge'!A7</f>
-        <v/>
-      </c>
-      <c r="B27">
-        <f>'Dairy Eggs Fridge'!B7</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>'Dairy Eggs Fridge'!D7</f>
-        <v/>
-      </c>
-      <c r="D27">
-        <f>'Dairy Eggs Fridge'!E7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <f>'Dairy Eggs Fridge'!A8</f>
-        <v/>
-      </c>
-      <c r="B28">
-        <f>'Dairy Eggs Fridge'!B8</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>'Dairy Eggs Fridge'!D8</f>
-        <v/>
-      </c>
-      <c r="D28">
-        <f>'Dairy Eggs Fridge'!E8</f>
-        <v/>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <f>'Dairy Eggs Fridge'!A9</f>
-        <v/>
-      </c>
-      <c r="B29">
-        <f>'Dairy Eggs Fridge'!B9</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>'Dairy Eggs Fridge'!D9</f>
-        <v/>
-      </c>
-      <c r="D29">
-        <f>'Dairy Eggs Fridge'!E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>'Dairy Eggs Fridge'!A10</f>
-        <v/>
-      </c>
-      <c r="B30">
-        <f>'Dairy Eggs Fridge'!B10</f>
-        <v/>
-      </c>
-      <c r="C30">
-        <f>'Dairy Eggs Fridge'!D10</f>
-        <v/>
-      </c>
-      <c r="D30">
-        <f>'Dairy Eggs Fridge'!E10</f>
-        <v/>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <f>'Dairy Eggs Fridge'!A11</f>
-        <v/>
-      </c>
-      <c r="B31">
-        <f>'Dairy Eggs Fridge'!B11</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>'Dairy Eggs Fridge'!D11</f>
-        <v/>
-      </c>
-      <c r="D31">
-        <f>'Dairy Eggs Fridge'!E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <f>'Dairy Eggs Fridge'!A12</f>
-        <v/>
-      </c>
-      <c r="B32">
-        <f>'Dairy Eggs Fridge'!B12</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>'Dairy Eggs Fridge'!D12</f>
-        <v/>
-      </c>
-      <c r="D32">
-        <f>'Dairy Eggs Fridge'!E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <f>'Dairy Eggs Fridge'!A13</f>
-        <v/>
-      </c>
-      <c r="B33">
-        <f>'Dairy Eggs Fridge'!B13</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>'Dairy Eggs Fridge'!D13</f>
-        <v/>
-      </c>
-      <c r="D33">
-        <f>'Dairy Eggs Fridge'!E13</f>
-        <v/>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <f>'Dairy Eggs Fridge'!A14</f>
-        <v/>
-      </c>
-      <c r="B34">
-        <f>'Dairy Eggs Fridge'!B14</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>'Dairy Eggs Fridge'!D14</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>'Dairy Eggs Fridge'!E14</f>
-        <v/>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <f>'Dairy Eggs Fridge'!A15</f>
-        <v/>
-      </c>
-      <c r="B35">
-        <f>'Dairy Eggs Fridge'!B15</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>'Dairy Eggs Fridge'!D15</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>'Dairy Eggs Fridge'!E15</f>
-        <v/>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <f>'Dairy Eggs Fridge'!A16</f>
-        <v/>
-      </c>
-      <c r="B36">
-        <f>'Dairy Eggs Fridge'!B16</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>'Dairy Eggs Fridge'!D16</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>'Dairy Eggs Fridge'!E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <f>'Dairy Eggs Fridge'!A17</f>
-        <v/>
-      </c>
-      <c r="B37">
-        <f>'Dairy Eggs Fridge'!B17</f>
-        <v/>
-      </c>
-      <c r="C37">
-        <f>'Dairy Eggs Fridge'!D17</f>
-        <v/>
-      </c>
-      <c r="D37">
-        <f>'Dairy Eggs Fridge'!E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <f>'Dairy Eggs Fridge'!A18</f>
-        <v/>
-      </c>
-      <c r="B38">
-        <f>'Dairy Eggs Fridge'!B18</f>
-        <v/>
-      </c>
-      <c r="C38">
-        <f>'Dairy Eggs Fridge'!D18</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>'Dairy Eggs Fridge'!E18</f>
-        <v/>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <f>'Dairy Eggs Fridge'!A19</f>
-        <v/>
-      </c>
-      <c r="B39">
-        <f>'Dairy Eggs Fridge'!B19</f>
-        <v/>
-      </c>
-      <c r="C39">
-        <f>'Dairy Eggs Fridge'!D19</f>
-        <v/>
-      </c>
-      <c r="D39">
-        <f>'Dairy Eggs Fridge'!E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <f>'Dairy Eggs Fridge'!A20</f>
-        <v/>
-      </c>
-      <c r="B40">
-        <f>'Dairy Eggs Fridge'!B20</f>
-        <v/>
-      </c>
-      <c r="C40">
-        <f>'Dairy Eggs Fridge'!D20</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>'Dairy Eggs Fridge'!E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <f>'Dairy Eggs Fridge'!A21</f>
-        <v/>
-      </c>
-      <c r="B41">
-        <f>'Dairy Eggs Fridge'!B21</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>'Dairy Eggs Fridge'!D21</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>'Dairy Eggs Fridge'!E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <f>'Dairy Eggs Fridge'!A22</f>
-        <v/>
-      </c>
-      <c r="B42">
-        <f>'Dairy Eggs Fridge'!B22</f>
-        <v/>
-      </c>
-      <c r="C42">
-        <f>'Dairy Eggs Fridge'!D22</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>'Dairy Eggs Fridge'!E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <f>'Dairy Eggs Fridge'!A23</f>
-        <v/>
-      </c>
-      <c r="B43">
-        <f>'Dairy Eggs Fridge'!B23</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>'Dairy Eggs Fridge'!D23</f>
-        <v/>
-      </c>
-      <c r="D43">
-        <f>'Dairy Eggs Fridge'!E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>'Dairy Eggs Fridge'!A24</f>
-        <v/>
-      </c>
-      <c r="B44">
-        <f>'Dairy Eggs Fridge'!B24</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>'Dairy Eggs Fridge'!D24</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>'Dairy Eggs Fridge'!E24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <f>'Dairy Eggs Fridge'!A25</f>
-        <v/>
-      </c>
-      <c r="B45">
-        <f>'Dairy Eggs Fridge'!B25</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>'Dairy Eggs Fridge'!D25</f>
-        <v/>
-      </c>
-      <c r="D45">
-        <f>'Dairy Eggs Fridge'!E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <f>'Dairy Eggs Fridge'!A26</f>
-        <v/>
-      </c>
-      <c r="B46">
-        <f>'Dairy Eggs Fridge'!B26</f>
-        <v/>
-      </c>
-      <c r="C46">
-        <f>'Dairy Eggs Fridge'!D26</f>
-        <v/>
-      </c>
-      <c r="D46">
-        <f>'Dairy Eggs Fridge'!E26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <f>'Dairy Eggs Fridge'!A27</f>
-        <v/>
-      </c>
-      <c r="B47">
-        <f>'Dairy Eggs Fridge'!B27</f>
-        <v/>
-      </c>
-      <c r="C47">
-        <f>'Dairy Eggs Fridge'!D27</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>'Dairy Eggs Fridge'!E27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <f>'Dairy Eggs Fridge'!A28</f>
-        <v/>
-      </c>
-      <c r="B48">
-        <f>'Dairy Eggs Fridge'!B28</f>
-        <v/>
-      </c>
-      <c r="C48">
-        <f>'Dairy Eggs Fridge'!D28</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>'Dairy Eggs Fridge'!E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <f>'Dairy Eggs Fridge'!A29</f>
-        <v/>
-      </c>
-      <c r="B49">
-        <f>'Dairy Eggs Fridge'!B29</f>
-        <v/>
-      </c>
-      <c r="C49">
-        <f>'Dairy Eggs Fridge'!D29</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>'Dairy Eggs Fridge'!E29</f>
-        <v/>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">avocado </t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">avocado </t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>Chocolate Biscuits</t>
+        </is>
+      </c>
+      <c r="D22" s="55" t="inlineStr">
+        <is>
+          <t>Hawaiian pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">green beans </t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">green beans </t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>Chocolate Peanut &amp; Almond Bar</t>
+        </is>
+      </c>
+      <c r="D23" s="55" t="inlineStr">
+        <is>
+          <t>Meat pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brown rice - whole grain </t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rice - whole grain </t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milk Chocolate Bar </t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>Sausage roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Eggs </t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>Original Potato Chips</t>
+        </is>
+      </c>
+      <c r="D25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chicken &amp; bacon pasta bake Pre Made </t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SNAP benefits US $48.50 , 25% of monthly allowance </t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cinnamon scroll </t>
+        </is>
+      </c>
+      <c r="C26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chocolate Cereal </t>
+        </is>
+      </c>
+      <c r="D26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Macaroni cheese Pre Made </t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justifies increased no of items for general population weekly shop </t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Short Cut Bacon </t>
+        </is>
+      </c>
+      <c r="C27" s="55" t="inlineStr">
+        <is>
+          <t>Frozen Hawaiian Pizza</t>
+        </is>
+      </c>
+      <c r="D27" s="55" t="inlineStr">
+        <is>
+          <t>Easy enchilada Pre Made</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>Chocolate Cereal</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Butter Chicken With Rice Pre Made </t>
+        </is>
+      </c>
+      <c r="D28" s="55" t="inlineStr">
+        <is>
+          <t>Chicken flavoured noodle cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Butter Chicken With Rice Pre Made </t>
+        </is>
+      </c>
+      <c r="C29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Macaroni Cheese Pre Made </t>
+        </is>
+      </c>
+      <c r="D29" s="55" t="inlineStr">
+        <is>
+          <t>Ramen noodle cup (mild)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>Hawaiin Pizza</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>French Cream Cheesecake</t>
+        </is>
+      </c>
+      <c r="D30" s="55" t="inlineStr">
+        <is>
+          <t>Frozen chocolate ice cream cones</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chocolate Oat Slices </t>
+        </is>
+      </c>
+      <c r="C31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flavoured Ice Blocks </t>
+        </is>
+      </c>
+      <c r="D31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flavoured Soda </t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Combined Justification 8.05.2026.xlsx
+++ b/Combined Justification 8.05.2026.xlsx
@@ -8760,13 +8760,11 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8789,9 +8787,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8814,9 +8809,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8839,8 +8831,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8868,9 +8858,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8893,9 +8880,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8955,7 +8939,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8988,9 +8971,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9013,9 +8993,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9038,9 +9015,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9063,9 +9037,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9088,9 +9059,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9113,9 +9081,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9148,7 +9113,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9171,9 +9135,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9196,9 +9157,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9221,9 +9179,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9246,9 +9201,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9271,9 +9223,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9296,9 +9245,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9321,9 +9267,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9346,9 +9289,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9413,7 +9353,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9441,9 +9380,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9466,9 +9402,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9491,9 +9424,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9516,9 +9446,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9541,7 +9468,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9574,9 +9500,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9599,9 +9522,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9624,9 +9544,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9649,9 +9566,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9674,9 +9588,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9699,9 +9610,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9724,9 +9632,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9749,8 +9654,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9778,9 +9681,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9803,9 +9703,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9828,9 +9725,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9853,9 +9747,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9878,9 +9769,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9903,9 +9791,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9928,9 +9813,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9953,9 +9835,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10015,17 +9894,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10048,9 +9916,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10073,9 +9938,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10098,9 +9960,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10123,9 +9982,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10148,9 +10004,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10173,9 +10026,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10198,9 +10048,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10223,9 +10070,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -10248,9 +10092,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10273,9 +10114,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10298,8 +10136,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10322,10 +10158,6 @@
           <t>Protein water citrus</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10348,9 +10180,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10373,9 +10202,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10398,9 +10224,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10423,9 +10246,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10448,8 +10268,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10477,9 +10295,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10502,9 +10317,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10527,9 +10339,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10552,9 +10361,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10577,13 +10383,11 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10606,9 +10410,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10631,9 +10432,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10656,9 +10454,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10681,9 +10476,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10706,9 +10498,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10731,7 +10520,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10764,9 +10552,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10789,9 +10574,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10814,9 +10596,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10839,9 +10618,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10864,9 +10640,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10889,7 +10662,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10922,8 +10694,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10951,13 +10721,11 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10980,9 +10748,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11005,9 +10770,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11030,9 +10792,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11060,7 +10819,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11088,9 +10846,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11113,9 +10868,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11138,9 +10890,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11163,9 +10912,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11188,9 +10934,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11213,9 +10956,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11238,9 +10978,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11268,8 +11005,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11329,9 +11064,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11354,9 +11086,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11379,9 +11108,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11404,9 +11130,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11429,9 +11152,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11454,9 +11174,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11479,9 +11196,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11504,9 +11218,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11529,9 +11240,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11554,9 +11262,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11579,9 +11284,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11604,9 +11306,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11629,9 +11328,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11654,9 +11350,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11679,9 +11372,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11704,9 +11394,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11729,9 +11416,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11791,9 +11475,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11816,9 +11497,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11841,9 +11519,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11866,9 +11541,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11891,9 +11563,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11916,8 +11585,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11945,9 +11612,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11970,8 +11634,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11999,9 +11661,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12024,9 +11683,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12049,9 +11705,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12074,9 +11727,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12099,9 +11749,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12124,8 +11771,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12153,9 +11798,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12215,9 +11857,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12240,9 +11879,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12270,8 +11906,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12294,9 +11928,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12319,9 +11950,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12344,9 +11972,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12369,9 +11994,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12394,9 +12016,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12419,9 +12038,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12444,13 +12060,11 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12473,9 +12087,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12498,13 +12109,11 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12527,9 +12136,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12552,9 +12158,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12577,9 +12180,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12602,9 +12202,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12627,21 +12224,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12664,9 +12246,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12689,9 +12268,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12714,9 +12290,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12739,9 +12312,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12764,9 +12334,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12826,9 +12393,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12851,9 +12415,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12876,9 +12437,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12901,9 +12459,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12926,9 +12481,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12956,8 +12508,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12980,9 +12530,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13005,9 +12552,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13030,9 +12574,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13055,9 +12596,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13080,9 +12618,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13105,9 +12640,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13130,9 +12662,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13160,8 +12689,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13184,9 +12711,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13209,9 +12733,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13234,9 +12755,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13259,9 +12777,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13284,9 +12799,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13309,9 +12821,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13334,9 +12843,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13359,9 +12865,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -13384,9 +12887,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13409,9 +12909,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -13434,9 +12931,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13459,9 +12953,16 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13484,9 +12985,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13509,9 +13007,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13534,9 +13029,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13564,8 +13056,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13588,9 +13078,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13613,9 +13100,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13638,9 +13122,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13663,9 +13144,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13688,9 +13166,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13713,9 +13188,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13738,9 +13210,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13763,9 +13232,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13788,9 +13254,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13813,9 +13276,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13838,9 +13298,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13863,9 +13320,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13888,9 +13342,21 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13913,9 +13379,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13938,9 +13401,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13963,9 +13423,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13988,9 +13445,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14013,8 +13467,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14042,8 +13494,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14071,9 +13521,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14096,9 +13543,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14121,9 +13565,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14146,9 +13587,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14171,9 +13609,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14196,9 +13631,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14221,9 +13653,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14246,9 +13675,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14271,9 +13697,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14306,7 +13729,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14329,9 +13751,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14354,7 +13773,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14387,8 +13805,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14416,9 +13832,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14441,9 +13854,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14466,8 +13876,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14495,9 +13903,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14520,9 +13925,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14545,9 +13947,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14570,9 +13969,6 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14595,9 +13991,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14630,7 +14023,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14653,9 +14045,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14688,7 +14077,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14711,9 +14099,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14746,7 +14131,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14779,7 +14163,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14802,9 +14185,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14827,9 +14207,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14857,8 +14234,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14881,9 +14256,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14906,9 +14278,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14931,9 +14300,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14961,8 +14327,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14985,9 +14349,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15010,9 +14371,6 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15045,7 +14403,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Combined Justification 8.05.2026.xlsx
+++ b/Combined Justification 8.05.2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="897" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="897" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sum of Primary Studies " sheetId="1" state="visible" r:id="rId1"/>
@@ -24,14 +24,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baskets" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,19 +108,6 @@
       <charset val="1"/>
       <color theme="1"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="PplxSans"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -237,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -266,30 +253,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -308,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -388,16 +351,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -412,32 +365,29 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -14749,90 +14699,90 @@
   </cols>
   <sheetData>
     <row r="1" ht="50.1" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="B1" s="46" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
         <is>
           <t>Coffino et al.
 2018</t>
         </is>
       </c>
-      <c r="C1" s="46" t="inlineStr">
+      <c r="C1" s="41" t="inlineStr">
         <is>
           <t>Coffino
 2020</t>
         </is>
       </c>
-      <c r="D1" s="46" t="inlineStr">
+      <c r="D1" s="41" t="inlineStr">
         <is>
           <t>Coffino
 2021</t>
         </is>
       </c>
-      <c r="E1" s="46" t="inlineStr">
+      <c r="E1" s="41" t="inlineStr">
         <is>
           <t>Anzman-Frasca
 2023</t>
         </is>
       </c>
-      <c r="F1" s="46" t="inlineStr">
+      <c r="F1" s="41" t="inlineStr">
         <is>
           <t>Ferrante et al.
 2024
 (secondary analysis)</t>
         </is>
       </c>
-      <c r="G1" s="46" t="inlineStr">
+      <c r="G1" s="41" t="inlineStr">
         <is>
           <t>Melo Herrera
 et al. 2024</t>
         </is>
       </c>
-      <c r="H1" s="46" t="inlineStr">
+      <c r="H1" s="41" t="inlineStr">
         <is>
           <t>Anzman-Frasca
 2026</t>
         </is>
       </c>
-      <c r="I1" s="47" t="inlineStr">
+      <c r="I1" s="42" t="inlineStr">
         <is>
           <t>MY STUDY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>CART &amp; TASK DESIGN</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="50" t="n"/>
-      <c r="D2" s="50" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="50" t="n"/>
-      <c r="G2" s="50" t="n"/>
-      <c r="H2" s="50" t="n"/>
-      <c r="I2" s="49" t="n"/>
+      <c r="B2" s="44" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="44" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>Catalog size
 (items available)</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="52" t="n"/>
-      <c r="I3" s="53" t="inlineStr">
+      <c r="B3" s="47" t="n"/>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="47" t="n"/>
+      <c r="E3" s="47" t="n"/>
+      <c r="F3" s="47" t="n"/>
+      <c r="G3" s="47" t="n"/>
+      <c r="H3" s="47" t="n"/>
+      <c r="I3" s="48" t="inlineStr">
         <is>
           <t>240 items
 10 categories</t>
@@ -14840,30 +14790,30 @@
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Items per session
 (typical selection)</t>
         </is>
       </c>
-      <c r="B4" s="54" t="n"/>
-      <c r="C4" s="54" t="inlineStr">
+      <c r="B4" s="49" t="n"/>
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>30 (with qty)
 23 (without qty)</t>
         </is>
       </c>
-      <c r="D4" s="54" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>21 (without qty)
 ~25 (with qty)</t>
         </is>
       </c>
-      <c r="E4" s="54" t="n"/>
-      <c r="F4" s="54" t="n"/>
-      <c r="G4" s="54" t="n"/>
-      <c r="H4" s="54" t="n"/>
-      <c r="I4" s="53" t="inlineStr">
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="49" t="n"/>
+      <c r="G4" s="49" t="n"/>
+      <c r="H4" s="49" t="n"/>
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>Up to 30
 (participant chooses)</t>
@@ -14871,28 +14821,28 @@
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Quantity selection
 (can select &gt;1 of same item)</t>
         </is>
       </c>
-      <c r="B5" s="52" t="n"/>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E5" s="52" t="n"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="52" t="n"/>
-      <c r="H5" s="52" t="n"/>
-      <c r="I5" s="53" t="inlineStr">
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="48" t="inlineStr">
         <is>
           <t>No
 (presence/absence only)</t>
@@ -14900,66 +14850,66 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Cart maximum
 (hard cap on selections)</t>
         </is>
       </c>
-      <c r="B6" s="54" t="n"/>
-      <c r="C6" s="54" t="n"/>
-      <c r="D6" s="54" t="n"/>
-      <c r="E6" s="54" t="n"/>
-      <c r="F6" s="54" t="n"/>
-      <c r="G6" s="54" t="n"/>
-      <c r="H6" s="54" t="n"/>
-      <c r="I6" s="53" t="inlineStr">
+      <c r="B6" s="49" t="n"/>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="48" t="inlineStr">
         <is>
           <t>30 items</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>BUDGET &amp; FINANCIAL</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n"/>
-      <c r="C7" s="49" t="n"/>
-      <c r="D7" s="49" t="n"/>
-      <c r="E7" s="49" t="n"/>
-      <c r="F7" s="49" t="n"/>
-      <c r="G7" s="49" t="n"/>
-      <c r="H7" s="49" t="n"/>
-      <c r="I7" s="49" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
+      <c r="I7" s="44" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Budget per session</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>$45 USD</t>
         </is>
       </c>
-      <c r="C8" s="54" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>$48.50 USD</t>
         </is>
       </c>
-      <c r="D8" s="54" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>$48.50 USD
 (~25% of monthly
 SNAP allowance)</t>
         </is>
       </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n"/>
-      <c r="G8" s="54" t="inlineStr">
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="inlineStr">
         <is>
           <t>$25/child/month
 $47/month
@@ -14967,83 +14917,83 @@
 breastfeeding)</t>
         </is>
       </c>
-      <c r="H8" s="54" t="n"/>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="48" t="inlineStr">
         <is>
           <t>No budget constraint</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Benefit programme</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="B9" s="47" t="n"/>
+      <c r="C9" s="47" t="n"/>
+      <c r="D9" s="47" t="inlineStr">
         <is>
           <t>SNAP</t>
         </is>
       </c>
-      <c r="E9" s="52" t="n"/>
-      <c r="F9" s="52" t="n"/>
-      <c r="G9" s="52" t="inlineStr">
+      <c r="E9" s="47" t="n"/>
+      <c r="F9" s="47" t="n"/>
+      <c r="G9" s="47" t="inlineStr">
         <is>
           <t>WIC</t>
         </is>
       </c>
-      <c r="H9" s="52" t="n"/>
-      <c r="I9" s="53" t="inlineStr">
+      <c r="H9" s="47" t="n"/>
+      <c r="I9" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>DEFAULT / PRE-LOADED CART</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="49" t="n"/>
-      <c r="G10" s="49" t="n"/>
-      <c r="H10" s="49" t="n"/>
-      <c r="I10" s="49" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
+      <c r="I10" s="44" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Example cart
 shown to participant</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="52" t="n"/>
-      <c r="E11" s="52" t="n"/>
-      <c r="F11" s="52" t="inlineStr">
+      <c r="C11" s="47" t="n"/>
+      <c r="D11" s="47" t="n"/>
+      <c r="E11" s="47" t="n"/>
+      <c r="F11" s="47" t="inlineStr">
         <is>
           <t>Yes
 (fruit only, 5 items)</t>
         </is>
       </c>
-      <c r="G11" s="52" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="52" t="n"/>
-      <c r="I11" s="53" t="inlineStr">
+      <c r="H11" s="47" t="n"/>
+      <c r="I11" s="48" t="inlineStr">
         <is>
           <t>Yes
 (pre-selected by condition)</t>
@@ -15051,31 +15001,31 @@
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Pre-selected items</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C12" s="54" t="n"/>
-      <c r="D12" s="54" t="n"/>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="54" t="inlineStr">
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="inlineStr">
         <is>
           <t>5 fruit items</t>
         </is>
       </c>
-      <c r="G12" s="54" t="inlineStr">
+      <c r="G12" s="49" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H12" s="54" t="n"/>
-      <c r="I12" s="53" t="inlineStr">
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="48" t="inlineStr">
         <is>
           <t>2 items per category
 per basket condition</t>
@@ -15083,20 +15033,20 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Basket conditions
 (# of distinct default carts)</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52" t="n"/>
-      <c r="G13" s="52" t="n"/>
-      <c r="H13" s="52" t="n"/>
-      <c r="I13" s="53" t="inlineStr">
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="47" t="n"/>
+      <c r="D13" s="47" t="n"/>
+      <c r="E13" s="47" t="n"/>
+      <c r="F13" s="47" t="n"/>
+      <c r="G13" s="47" t="n"/>
+      <c r="H13" s="47" t="n"/>
+      <c r="I13" s="48" t="inlineStr">
         <is>
           <t>4 conditions:
 healthy_a, healthy_b
@@ -15105,48 +15055,48 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>STUDY DESIGN</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="49" t="n"/>
-      <c r="G14" s="49" t="n"/>
-      <c r="H14" s="49" t="n"/>
-      <c r="I14" s="49" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
+      <c r="I14" s="44" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Sessions / time points</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="inlineStr">
+      <c r="B15" s="47" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="47" t="inlineStr">
         <is>
           <t>5 time points</t>
         </is>
       </c>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
-      <c r="G15" s="52" t="inlineStr">
+      <c r="E15" s="47" t="n"/>
+      <c r="F15" s="47" t="n"/>
+      <c r="G15" s="47" t="inlineStr">
         <is>
           <t>Items to last
 10 days</t>
         </is>
       </c>
-      <c r="H15" s="52" t="inlineStr">
+      <c r="H15" s="47" t="inlineStr">
         <is>
           <t>2 intervention
 weeks</t>
         </is>
       </c>
-      <c r="I15" s="53" t="inlineStr">
+      <c r="I15" s="48" t="inlineStr">
         <is>
           <t>1
 (single-session survey)</t>
@@ -15154,170 +15104,170 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>RECIPE COMPONENT</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="49" t="n"/>
-      <c r="G16" s="49" t="n"/>
-      <c r="H16" s="49" t="n"/>
-      <c r="I16" s="49" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="44" t="n"/>
+      <c r="I16" s="44" t="n"/>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Recipe intervention</t>
         </is>
       </c>
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="inlineStr">
+      <c r="C17" s="47" t="n"/>
+      <c r="D17" s="47" t="n"/>
+      <c r="E17" s="47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="52" t="inlineStr">
+      <c r="F17" s="47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="52" t="inlineStr">
+      <c r="G17" s="47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" s="52" t="inlineStr">
+      <c r="H17" s="47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I17" s="53" t="inlineStr">
+      <c r="I17" s="48" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="46" t="inlineStr">
         <is>
           <t>Recipes per week</t>
         </is>
       </c>
-      <c r="B18" s="54" t="n"/>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="54" t="n"/>
-      <c r="E18" s="54" t="inlineStr">
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F18" s="54" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G18" s="54" t="n"/>
-      <c r="H18" s="54" t="inlineStr">
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I18" s="53" t="n"/>
+      <c r="I18" s="48" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="51" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Avg ingredients
 per recipe</t>
         </is>
       </c>
-      <c r="B19" s="52" t="n"/>
-      <c r="C19" s="52" t="n"/>
-      <c r="D19" s="52" t="n"/>
-      <c r="E19" s="52" t="inlineStr">
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="47" t="n"/>
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>~10.2
 (163 total ÷ 16 recipes)</t>
         </is>
       </c>
-      <c r="F19" s="52" t="n"/>
-      <c r="G19" s="52" t="inlineStr">
+      <c r="F19" s="47" t="n"/>
+      <c r="G19" s="47" t="inlineStr">
         <is>
           <t>~10
 (30/week ÷ 3)</t>
         </is>
       </c>
-      <c r="H19" s="52" t="inlineStr">
+      <c r="H19" s="47" t="inlineStr">
         <is>
           <t>~9.7
 (12 + 8 + 9 ÷ 3)</t>
         </is>
       </c>
-      <c r="I19" s="53" t="n"/>
+      <c r="I19" s="48" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Total ingredients
 per week</t>
         </is>
       </c>
-      <c r="B20" s="54" t="n"/>
-      <c r="C20" s="54" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="54" t="inlineStr">
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>~30.6</t>
         </is>
       </c>
-      <c r="F20" s="54" t="n"/>
-      <c r="G20" s="54" t="inlineStr">
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="inlineStr">
         <is>
           <t>~30</t>
         </is>
       </c>
-      <c r="H20" s="54" t="inlineStr">
+      <c r="H20" s="49" t="inlineStr">
         <is>
           <t>30
 (+ fruit &amp; veg serving)</t>
         </is>
       </c>
-      <c r="I20" s="53" t="n"/>
+      <c r="I20" s="48" t="n"/>
     </row>
     <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Recipe notes</t>
         </is>
       </c>
-      <c r="B21" s="52" t="n"/>
-      <c r="C21" s="52" t="n"/>
-      <c r="D21" s="52" t="n"/>
-      <c r="E21" s="52" t="inlineStr">
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="47" t="n"/>
+      <c r="E21" s="47" t="inlineStr">
         <is>
           <t>16 recipe options in
 supplementary data;
 163 ingredient entries total</t>
         </is>
       </c>
-      <c r="F21" s="52" t="inlineStr">
+      <c r="F21" s="47" t="inlineStr">
         <is>
           <t>Secondary analysis;
 sample cart fruit-only</t>
         </is>
       </c>
-      <c r="G21" s="52" t="n"/>
-      <c r="H21" s="52" t="inlineStr">
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="inlineStr">
         <is>
           <t>Recipe 1: 12 ingredients
 Recipe 2: 8 ingredients
@@ -15325,37 +15275,37 @@
 +fruit/veg serving</t>
         </is>
       </c>
-      <c r="I21" s="53" t="n"/>
+      <c r="I21" s="48" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>HEALTH CLASSIFICATION</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="49" t="n"/>
-      <c r="G22" s="49" t="n"/>
-      <c r="H22" s="49" t="n"/>
-      <c r="I22" s="49" t="n"/>
+      <c r="B22" s="44" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+      <c r="F22" s="44" t="n"/>
+      <c r="G22" s="44" t="n"/>
+      <c r="H22" s="44" t="n"/>
+      <c r="I22" s="44" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="46" t="inlineStr">
         <is>
           <t>Classification method</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n"/>
-      <c r="C23" s="52" t="n"/>
-      <c r="D23" s="52" t="n"/>
-      <c r="E23" s="52" t="n"/>
-      <c r="F23" s="52" t="n"/>
-      <c r="G23" s="52" t="n"/>
-      <c r="H23" s="52" t="n"/>
-      <c r="I23" s="53" t="inlineStr">
+      <c r="B23" s="47" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="47" t="n"/>
+      <c r="E23" s="47" t="n"/>
+      <c r="F23" s="47" t="n"/>
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
+      <c r="I23" s="48" t="inlineStr">
         <is>
           <t>Binary per item:
 healthy / unhealthy</t>
@@ -15363,19 +15313,19 @@
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>Health outcome measure</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="54" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="54" t="n"/>
-      <c r="I24" s="53" t="inlineStr">
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="48" t="inlineStr">
         <is>
           <t>Health score =
 % healthy items
@@ -15398,7 +15348,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.85546875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16.7109375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="26.42578125" customWidth="1" style="1" min="2" max="2"/>
     <col width="19.42578125" customWidth="1" style="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="1" min="4" max="4"/>
   </cols>
@@ -15477,7 +15427,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>cucumber</t>
+          <t>Cucumber</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -15499,7 +15449,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>red onion</t>
+          <t>Brown onion</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -15521,7 +15471,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Whole Grain wraps</t>
+          <t>Wholemeal wrap</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -15543,7 +15493,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organic Peanut butter </t>
+          <t xml:space="preserve">Organic peanut butter </t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -15565,7 +15515,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lean Mince Meat </t>
+          <t>Lean beef mince</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -15573,7 +15523,7 @@
           <t>sweet potatoes</t>
         </is>
       </c>
-      <c r="D8" s="55" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Cinnamon scroll </t>
         </is>
@@ -15587,7 +15537,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicken breast </t>
+          <t>Chicken breast fillet</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -15595,7 +15545,7 @@
           <t xml:space="preserve">bananas </t>
         </is>
       </c>
-      <c r="D9" s="55" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>Butter croissant</t>
         </is>
@@ -15609,7 +15559,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweet potatoes </t>
+          <t>Sweet potatoe</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -15617,7 +15567,7 @@
           <t xml:space="preserve">carrots </t>
         </is>
       </c>
-      <c r="D10" s="55" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>Double choc muffins</t>
         </is>
@@ -15631,7 +15581,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bananas </t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -15639,7 +15589,7 @@
           <t>canned black beans low sodium</t>
         </is>
       </c>
-      <c r="D11" s="55" t="inlineStr">
+      <c r="D11" s="50" t="inlineStr">
         <is>
           <t>Chocolate coated biscuits</t>
         </is>
@@ -15653,7 +15603,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">mushrooms </t>
+          <t>Reduced fat milk</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -15661,7 +15611,7 @@
           <t xml:space="preserve">whole wheat spagehtti </t>
         </is>
       </c>
-      <c r="D12" s="55" t="inlineStr">
+      <c r="D12" s="50" t="inlineStr">
         <is>
           <t>Mix lollies</t>
         </is>
@@ -15675,7 +15625,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrots </t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -15683,7 +15633,7 @@
           <t>frozen mix veg</t>
         </is>
       </c>
-      <c r="D13" s="55" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Chocolate Oat Slices </t>
         </is>
@@ -15697,7 +15647,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -15705,7 +15655,7 @@
           <t xml:space="preserve">protein greek yoghurt </t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr">
+      <c r="D14" s="50" t="inlineStr">
         <is>
           <t>Chocolate cereal</t>
         </is>
@@ -15719,7 +15669,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">canned black beans low sodium </t>
+          <t xml:space="preserve">Black beans reduced salt </t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -15727,7 +15677,7 @@
           <t xml:space="preserve">tuna in spring water </t>
         </is>
       </c>
-      <c r="D15" s="55" t="inlineStr">
+      <c r="D15" s="50" t="inlineStr">
         <is>
           <t>Triple Chocolate chip yoghurt</t>
         </is>
@@ -15741,7 +15691,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole wheat spaghetti </t>
+          <t xml:space="preserve">Spaghetti </t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -15749,7 +15699,7 @@
           <t xml:space="preserve">free range eggs </t>
         </is>
       </c>
-      <c r="D16" s="55" t="inlineStr">
+      <c r="D16" s="50" t="inlineStr">
         <is>
           <t>Original potato chips</t>
         </is>
@@ -15763,15 +15713,15 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">frozen broccoli </t>
-        </is>
-      </c>
-      <c r="C17" s="55" t="inlineStr">
+          <t xml:space="preserve">Frozen broccoli </t>
+        </is>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Cinnamon scroll </t>
         </is>
       </c>
-      <c r="D17" s="55" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>Short cut bacon</t>
         </is>
@@ -15785,15 +15735,15 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">frozen mix veg </t>
-        </is>
-      </c>
-      <c r="C18" s="55" t="inlineStr">
+          <t>Frozen vegtable mix</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Double Choc Muffin </t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>Champagne leg ham</t>
         </is>
@@ -15807,15 +15757,15 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolognase sauce traditional </t>
-        </is>
-      </c>
-      <c r="C19" s="55" t="inlineStr">
+          <t>Bolognase sauce</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>Apple Crown Danish</t>
         </is>
       </c>
-      <c r="D19" s="55" t="inlineStr">
+      <c r="D19" s="50" t="inlineStr">
         <is>
           <t>Deli continental chorizo</t>
         </is>
@@ -15832,12 +15782,12 @@
           <t xml:space="preserve">Protein Greek Yoghurt </t>
         </is>
       </c>
-      <c r="C20" s="55" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>Short Cut Bacon</t>
         </is>
       </c>
-      <c r="D20" s="55" t="inlineStr">
+      <c r="D20" s="50" t="inlineStr">
         <is>
           <t>Thin BBQ sausages</t>
         </is>
@@ -15851,15 +15801,15 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">tuna in spring water </t>
-        </is>
-      </c>
-      <c r="C21" s="55" t="inlineStr">
+          <t xml:space="preserve">Tuna in spring water </t>
+        </is>
+      </c>
+      <c r="C21" s="50" t="inlineStr">
         <is>
           <t>Champagne Leg Ham</t>
         </is>
       </c>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
         <is>
           <t>Beef burger patties</t>
         </is>
@@ -15873,15 +15823,15 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">avocado </t>
-        </is>
-      </c>
-      <c r="C22" s="55" t="inlineStr">
+          <t>Rye bread</t>
+        </is>
+      </c>
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>Chocolate Biscuits</t>
         </is>
       </c>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="50" t="inlineStr">
         <is>
           <t>Hawaiian pizza</t>
         </is>
@@ -15895,15 +15845,15 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">green beans </t>
-        </is>
-      </c>
-      <c r="C23" s="55" t="inlineStr">
+          <t xml:space="preserve">Green beans </t>
+        </is>
+      </c>
+      <c r="C23" s="50" t="inlineStr">
         <is>
           <t>Chocolate Peanut &amp; Almond Bar</t>
         </is>
       </c>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>Meat pie</t>
         </is>
@@ -15917,15 +15867,15 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rice - whole grain </t>
-        </is>
-      </c>
-      <c r="C24" s="55" t="inlineStr">
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C24" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Milk Chocolate Bar </t>
         </is>
       </c>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="50" t="inlineStr">
         <is>
           <t>Sausage roll</t>
         </is>
@@ -15937,12 +15887,12 @@
           <t xml:space="preserve"> Eggs </t>
         </is>
       </c>
-      <c r="C25" s="55" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>Original Potato Chips</t>
         </is>
       </c>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Chicken &amp; bacon pasta bake Pre Made </t>
         </is>
@@ -15954,17 +15904,17 @@
           <t xml:space="preserve">SNAP benefits US $48.50 , 25% of monthly allowance </t>
         </is>
       </c>
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B26" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Cinnamon scroll </t>
         </is>
       </c>
-      <c r="C26" s="55" t="inlineStr">
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Chocolate Cereal </t>
         </is>
       </c>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Macaroni cheese Pre Made </t>
         </is>
@@ -15976,85 +15926,85 @@
           <t xml:space="preserve">Justifies increased no of items for general population weekly shop </t>
         </is>
       </c>
-      <c r="B27" s="55" t="inlineStr">
+      <c r="B27" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Short Cut Bacon </t>
         </is>
       </c>
-      <c r="C27" s="55" t="inlineStr">
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>Frozen Hawaiian Pizza</t>
         </is>
       </c>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="50" t="inlineStr">
         <is>
           <t>Easy enchilada Pre Made</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="55" t="inlineStr">
-        <is>
-          <t>Chocolate Cereal</t>
-        </is>
-      </c>
-      <c r="C28" s="55" t="inlineStr">
+      <c r="B28" s="50" t="inlineStr">
+        <is>
+          <t>Chocolate flavoured cereal</t>
+        </is>
+      </c>
+      <c r="C28" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Butter Chicken With Rice Pre Made </t>
         </is>
       </c>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="50" t="inlineStr">
         <is>
           <t>Chicken flavoured noodle cup</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
-      <c r="B29" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Butter Chicken With Rice Pre Made </t>
-        </is>
-      </c>
-      <c r="C29" s="55" t="inlineStr">
+      <c r="B29" s="50" t="inlineStr">
+        <is>
+          <t>Butter Chicken With Rice</t>
+        </is>
+      </c>
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Macaroni Cheese Pre Made </t>
         </is>
       </c>
-      <c r="D29" s="55" t="inlineStr">
+      <c r="D29" s="50" t="inlineStr">
         <is>
           <t>Ramen noodle cup (mild)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="55" t="inlineStr">
+      <c r="B30" s="50" t="inlineStr">
         <is>
           <t>Hawaiin Pizza</t>
         </is>
       </c>
-      <c r="C30" s="55" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>French Cream Cheesecake</t>
         </is>
       </c>
-      <c r="D30" s="55" t="inlineStr">
+      <c r="D30" s="50" t="inlineStr">
         <is>
           <t>Frozen chocolate ice cream cones</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="55" t="inlineStr">
+      <c r="B31" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Chocolate Oat Slices </t>
         </is>
       </c>
-      <c r="C31" s="55" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Flavoured Ice Blocks </t>
         </is>
       </c>
-      <c r="D31" s="55" t="inlineStr">
+      <c r="D31" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Flavoured Soda </t>
         </is>
@@ -16071,152 +16021,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B251"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bakery (19 items)</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bakery (19 items)</t>
+          <t>Apple danish</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apple danish</t>
+          <t>Multigrain bread</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Multigrain bread</t>
+          <t>Double choc muffin</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Double Choc Muffin</t>
+          <t>Butter croissant</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Butter croissant</t>
+          <t>High fibre white bread</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>High fibre white bread</t>
+          <t>Choc Chip hot cross bun</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Choc Chip hot cross bun</t>
+          <t>Wholemeal roll</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wholemeal Roll</t>
+          <t>Rye bread</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rye Bread</t>
+          <t>Fruit filled tart</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fruit filled tart</t>
+          <t>Wholemeal bread</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wholemeal bread</t>
+          <t>Jam filled doughnut</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jam filled doughnut</t>
+          <t>Wholemeal english muffin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wholemeal english muffin</t>
+          <t>Bagel plain</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagel Plain</t>
+          <t>Ham &amp; cheese croissant</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ham &amp; Cheese Croissant</t>
+          <t>Cheese &amp; bacon roll</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cheese &amp; Bacon Roll</t>
+          <t>Cinnamon scroll</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cinnamon scroll</t>
+          <t>BBQ cheese &amp; bacon roll</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>BBQ Cheese &amp; Bacon Roll</t>
+          <t>Wholemeal pizza base</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wholemeal Pizza Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Wholemeal Wrap</t>
-        </is>
-      </c>
-    </row>
+          <t>Wholemeal wrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
@@ -16227,7 +16178,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Champagne Leg Ham</t>
+          <t>Leg ham</t>
         </is>
       </c>
     </row>
@@ -16269,14 +16220,14 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chicken Breast Thinly Sliced</t>
+          <t>Chicken breast sliced</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fresh Carbonara Pasta Sauce</t>
+          <t>Fresh carbonara pasta sauce</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16255,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Soy Milk</t>
+          <t>Soy milk</t>
         </is>
       </c>
     </row>
@@ -16374,14 +16325,14 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reduced Fat Cheddar Cheese</t>
+          <t>Reduced fat cheddar cheese</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>High Protein Chocolate Pudding</t>
+          <t>High protein chocolate pudding</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16353,7 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fresh Napoli Sauce</t>
+          <t>Fresh napoli sauce</t>
         </is>
       </c>
     </row>
@@ -16416,1412 +16367,1420 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>Short Cut Bacon</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Drinks (13 items)</t>
-        </is>
-      </c>
-    </row>
+          <t>Short cut bacon</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>Natural spring water</t>
+          <t>Drinks (13 items)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tropical punch juice</t>
+          <t>Natural spring water</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>Electrolyte sport drink</t>
+          <t>Tropical punch juice</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>High protein chocolate shake</t>
+          <t>Electrolyte sport drink</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>Protein water citrus</t>
+          <t>High protein chocolate shake</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lightly sparkling water</t>
+          <t>Protein water citrus</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>Orange juice</t>
+          <t>Lightly sparkling water</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>Flavoured water wildberry</t>
+          <t>Orange juice</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>Protein water berry</t>
+          <t>Flavoured water wildberry</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cola flavoured soda</t>
+          <t>Protein water berry</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>Soda water</t>
+          <t>Cola flavoured soda</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chocolate flavoured coconut water</t>
+          <t>Soda water</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>Energy Drink</t>
+          <t>Chocolate flavoured coconut water</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>Frozen (29 items)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Frozen mixed berries</t>
-        </is>
-      </c>
-    </row>
+          <t>Energy drink</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>Frozen Peas</t>
+          <t>Frozen (29 items)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>French Cream Cheesecake</t>
+          <t>Frozen mixed berries</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shortcrust Pastry</t>
+          <t>Frozen Peas</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>Icecream cake</t>
+          <t>French Cream Cheesecake</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>Frozen mango</t>
+          <t>Shortcrust Pastry</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>Frozen Beans</t>
+          <t>Icecream cake</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tiramisu</t>
+          <t>Frozen mango</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>Beef Curry Puff</t>
+          <t>Frozen beans</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>Strawberry cheesecake</t>
+          <t>Tiramisu</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frozen strawberries</t>
+          <t>Beef curry puff</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chinese Stir Fry Mix Veg</t>
+          <t>Strawberry cheesecake</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>Meatlovers Pizza</t>
+          <t>Frozen strawberries</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quiche Cheese &amp; Bacon</t>
+          <t>Chinese stir fry mix veg</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>Strawberry icecream</t>
+          <t>Meatlovers pizza</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frozen Broccoli</t>
+          <t>Quiche cheese &amp; bacon</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>Frozen Carrots</t>
+          <t>Strawberry icecream</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cheese &amp; Bacon Pizza</t>
+          <t>Frozen broccoli</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dim Sim</t>
+          <t>Frozen carrots</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vanilla icecream</t>
+          <t>Cheese &amp; bacon pizza</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>Frozen Vegetable Mix</t>
+          <t>Dim sim</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>Flavoured Iceblocks</t>
+          <t>Vanilla icecream</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hawaiin Pizza</t>
+          <t>Frozen vegetable mix</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chocolate Bavarian</t>
+          <t>Flavoured iceblocks</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>Apple pie</t>
+          <t>Hawaiin pizza</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>Frozen Cauliflower</t>
+          <t>Chocolate bavarian</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chocolate icecream</t>
+          <t>Apple pie</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>Puff Pastry Sheets</t>
+          <t>Frozen cauliflower</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chocolate cake</t>
+          <t>Chocolate icecream</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fruit (20 items)</t>
+          <t>Puff pastry sheet</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nectarine</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>blueberries</t>
-        </is>
-      </c>
-    </row>
+          <t>Chocolate cake</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bannanas</t>
+          <t>Fruit (20 items)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>Canned fruit salad</t>
+          <t>Nectarine</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>Freeze dried fruit dipped in chocolate</t>
+          <t>Blueberry</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>pears</t>
+          <t>Canned fruit salad</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Freeze dried fruit dipped in chocolate</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dried apple</t>
+          <t>Grape</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fruit Jelly Cup</t>
+          <t>Pear</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>Watermelon</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>Dried apple</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kiwi fruit</t>
+          <t>Fruit Jelly Cup</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dried mango</t>
+          <t>Watermelon</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fruit string</t>
+          <t>Pineapple</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>Strawberries</t>
+          <t>Kiwi fruit</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Dried mango</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>Canned peaches</t>
+          <t>Fruit string</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>Banana Chips</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fruit roll up</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>Meat Seafood (22 items)</t>
+          <t>Canned peache</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>Extra lean beef mince</t>
+          <t>Banana Chip</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kangaroo diced</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Barramundi</t>
-        </is>
-      </c>
-    </row>
+          <t>Fruit roll up</t>
+        </is>
+      </c>
+    </row>
+    <row r="119"/>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>Beef burgers patties</t>
+          <t>Meat Seafood (22 items)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>Beef brisket burgers</t>
+          <t>Lean beef mince</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Kangaroo diced</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chicken breast fillets</t>
+          <t>Barramundi</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tuna steaks</t>
+          <t>Beef burgers pattie</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lamb burgers</t>
+          <t>Beef brisket burgers</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>Beef chevap</t>
+          <t>Steak</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lamb leg diced</t>
+          <t>Chicken breast fillet</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>Turkey mince</t>
+          <t>Tuna steak</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>Thin Bbq sausages</t>
+          <t>Lamb burger</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t>Beef Bbq burgers</t>
+          <t>Beef chevap</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deli continental chorizo</t>
+          <t>Lamb leg diced</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>Pork sizzle steaks</t>
+          <t>Turkey mince</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>Basa fillet</t>
+          <t>Thin Bbq sausage</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>Beef sausages</t>
+          <t>Beef Bbq burger</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kransky bites</t>
+          <t>Deli continental chorizo</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>Roll chicken</t>
+          <t>Pork sizzle steak</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>Extra lean pork mince</t>
+          <t>Basa fillet</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Beef sausage</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pantry (44 items)</t>
+          <t>Kransky bite</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bolognese sauce</t>
+          <t>Roll chicken</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pasta penne</t>
+          <t>Lean pork mince</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t>Whole green lentils</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Organic tomatoes canned</t>
-        </is>
-      </c>
-    </row>
+          <t>Salmon</t>
+        </is>
+      </c>
+    </row>
+    <row r="143"/>
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pappadams</t>
+          <t>Pantry (44 items)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t>Butter chicken sauce</t>
+          <t>Bolognese sauce</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>Glass noodles</t>
+          <t>Pasta penne</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lentil soup mix dried</t>
+          <t>Whole green lentils</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pumpkin seeds</t>
+          <t>Organic tomatoes canned</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chocolate flavoured cereal</t>
+          <t>Pappadams</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sweet and sour stir fry sauce</t>
+          <t>Butter chicken sauce</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cous cous</t>
+          <t>Glass noodle</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>Springwater tuna</t>
+          <t>Lentil soup mix dried</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>Black chia seeds</t>
+          <t>Pumpkin seed</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>Rainbow flavoured cereal</t>
+          <t>Chocolate flavoured cereal</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>Rogan josh sauce</t>
+          <t>Sweet and sour stir fry sauce</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tri colour quinoa</t>
+          <t>Cous cous</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sprinwater salmon</t>
+          <t>Tuna in springwater</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sunflower seeds</t>
+          <t>Black chia seed</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chocolate coated peanuts</t>
+          <t>Rainbow flavoured cereal</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tikka masala sauce</t>
+          <t>Rogan josh sauce</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>Kidney beans</t>
+          <t>Tri colour quinoa</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>Unsalted mixed nuts</t>
+          <t>Salmon in springwater</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>Walnuts</t>
+          <t>Sunflower seed</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>Choc coated almonds</t>
+          <t>Chocolate coated peanuts</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tortillas</t>
+          <t>Tikka masala sauce</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>Chick peas</t>
+          <t>Kidney beans</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>Unsalted cashews</t>
+          <t>Unsalted mixed nut</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>Almonds</t>
+          <t>Walnut</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t>Beef jerky</t>
+          <t>Choc coated almonds</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Tortilla</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t>Black beans</t>
+          <t>Chickpeas</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t>Organic peanut butter</t>
+          <t>Unsalted cashew</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t>Korma simmer sauce</t>
+          <t>Almond</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t>Chicken flavoured noodle cup</t>
+          <t>Beef jerky</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t>Long grain rice</t>
+          <t>Oats</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>Baked beans</t>
+          <t>Black beans reduced salt</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>Beetroot canned</t>
+          <t>Organic peanut butter</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vindaloo simmer sauce</t>
+          <t>Korma simmer sauce</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ramen noodle cup mild</t>
+          <t>Chicken flavoured noodle cup</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t>Pasta spaghetti</t>
+          <t>Rice</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t>Red lentils dried</t>
+          <t>Baked beans</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>Corn Kernels no added salt canned</t>
+          <t>Beetroot canned</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t>Honey soy stir fry sauce</t>
+          <t>Vindaloo simmer sauce</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ready to eat (20 items)</t>
+          <t>Ramen noodle cup mild</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lentil salad with olive oil</t>
+          <t>Spaghetti</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tomato &amp; basil soup</t>
+          <t>Red lentils dried</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ultra green soup</t>
+          <t>Corn Kernels no added salt canned</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t>Chicken &amp; bacon pasta bake</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Pastie</t>
-        </is>
-      </c>
-    </row>
+          <t>Honey soy stir fry sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="189"/>
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
-          <t>Green salad</t>
+          <t>Ready to eat (20 items)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="inlineStr">
         <is>
-          <t>Broccoli, cauliflower &amp; parmesan soup</t>
+          <t>Lentil salad with olive oil</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t>Butter chicken with rice</t>
+          <t>Tomato &amp; basil soup</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t>Protein BBQ chicken burrito</t>
+          <t>Ultra green soup</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t>Meat pie</t>
+          <t>Chicken &amp; bacon pasta bake</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chicken &amp; corn soup</t>
+          <t>Pastie</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="inlineStr">
         <is>
-          <t>Pea &amp; ham soup</t>
+          <t>Green salad</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
-          <t>Beef stroganoff with rice</t>
+          <t>Broccoli, cauliflower &amp; parmesan soup</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="inlineStr">
         <is>
-          <t>Pulled pork smokey chipolte burrito</t>
+          <t>Butter chicken with rice</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t>Microwaveable sausage Roll</t>
+          <t>Protein BBQ chicken burrito</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t>Chicken noodle soup</t>
+          <t>Meat pie</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t>Minestrone soup</t>
+          <t>Chicken &amp; corn soup</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t>Macaroni cheese</t>
+          <t>Pea &amp; ham soup</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t>Easy enchilada</t>
+          <t>Beef stroganoff with rice</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="inlineStr">
         <is>
-          <t>Samosa</t>
+          <t>Pulled pork smokey chipolte burrito</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="inlineStr">
         <is>
-          <t>Snacks (28 items)</t>
+          <t>Microwaveable sausage Roll</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="inlineStr">
         <is>
-          <t>Multigrain crackers and light cheese</t>
+          <t>Chicken noodle soup</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
-          <t>Jelly beans</t>
+          <t>Minestrone soup</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t>Snake lollies</t>
+          <t>Macaroni cheese</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t>Chocolate coated biscuits</t>
+          <t>Easy enchilada</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t>Crunchy oats &amp; honey bars</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Wholegrain rice crackers</t>
-        </is>
-      </c>
-    </row>
+          <t>Samosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="211"/>
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t>Liquorice</t>
+          <t>Snacks (28 items)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t>Plain crackers</t>
+          <t>Multigrain crackers and light cheese</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t>Chocolate cream wafers</t>
+          <t>Jelly bean</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t>Chocolate oat slices</t>
+          <t>Snake lollies</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="inlineStr">
         <is>
-          <t>Multigrain crispbread crackers</t>
+          <t>Chocolate coated biscuit</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
-          <t>Marshmallows</t>
+          <t>Crunchy oats &amp; honey bars</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t>Cheese corn chips</t>
+          <t>Wholegrain rice cracker</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nut bars chocolate peanut &amp; almond</t>
+          <t>Liquorice</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="B220" t="inlineStr">
         <is>
-          <t>Biscuits shortbread creams</t>
+          <t>Plain cracker</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t>Mini rice crisps milk chocolate</t>
+          <t>Chocolate cream wafer</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t>Milk chocolate</t>
+          <t>Chocolate oat slices</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t>Original potato chips</t>
+          <t>Multigrain crispbread cracker</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t>Rice bubbles snack bars</t>
+          <t>Marshmallow</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>Chicken flavoured potato chips</t>
+          <t>Cheese corn chip</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mix lollies</t>
+          <t>Nut bars chocolate peanut &amp; almond</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
-          <t>Hazelnut spread</t>
+          <t>Biscuits shortbread creams</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t>Choclate chip cookies</t>
+          <t>Rice crisps milk chocolate</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t>Flavoured rainbow Sticks</t>
+          <t>Milk chocolate</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t>Salt &amp; Vinegar chips</t>
+          <t>Original potato chip</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t>Jelly</t>
+          <t>Rice bubbles snack bar</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mayple syrup</t>
+          <t>Chicken flavoured potato chips</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t>Pretzels</t>
+          <t>Mix lollies</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t>Vegetables (17 items)</t>
+          <t>Hazelnut spread</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t>Broccoli</t>
+          <t>Choclate chip cookie</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t>Capsicum</t>
+          <t>Flavoured rainbow stick</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t>Cauliflower</t>
+          <t>Salt &amp; Vinegar chips</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t>Sweet corn</t>
+          <t>Jelly</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t>Eggplant</t>
+          <t>Mayple syrup</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t>Carrots</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Lettuce</t>
-        </is>
-      </c>
-    </row>
+          <t>Pretzel</t>
+        </is>
+      </c>
+    </row>
+    <row r="241"/>
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t>Brown onion</t>
+          <t>Vegetables (17 items)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t>Bok Choy</t>
+          <t>Broccoli</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t>Celery</t>
+          <t>Capsicum</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t>Zucchini</t>
+          <t>Cauliflower</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sweet potatoe</t>
+          <t>Sweet corn</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t>Pumpkin</t>
+          <t>Eggplant</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t>Cucumber</t>
+          <t>Lettuce</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t>tomatoes</t>
+          <t>Brown onion</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="B251" t="inlineStr">
+        <is>
+          <t>Bok Choy</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Celery</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Zucchini</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Sweet potatoe</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Pumpkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Green beans</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Potatoe</t>
         </is>
@@ -19136,218 +19095,218 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>DEF1</t>
         </is>
       </c>
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="38" t="inlineStr">
         <is>
           <t>Pauls Low Fat Less Sugar Vanilla Custard | 600g</t>
         </is>
       </c>
-      <c r="D2" s="42" t="inlineStr">
+      <c r="D2" s="38" t="inlineStr">
         <is>
           <t>Reduced fat custard</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
+      <c r="E2" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F2" s="43" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>1.0 g</t>
         </is>
       </c>
-      <c r="G2" s="39" t="inlineStr">
+      <c r="G2" s="35" t="inlineStr">
         <is>
           <t>79 mg</t>
         </is>
       </c>
-      <c r="H2" s="39" t="inlineStr">
+      <c r="H2" s="35" t="inlineStr">
         <is>
           <t>0.1 g</t>
         </is>
       </c>
-      <c r="I2" s="39" t="inlineStr">
+      <c r="I2" s="35" t="inlineStr">
         <is>
           <t>9.3 g</t>
         </is>
       </c>
-      <c r="J2" s="39" t="inlineStr">
+      <c r="J2" s="35" t="inlineStr">
         <is>
           <t>149 mg</t>
         </is>
       </c>
-      <c r="K2" s="43" t="inlineStr">
+      <c r="K2" s="39" t="inlineStr">
         <is>
           <t>Reduced-fat varieties are green.</t>
         </is>
       </c>
-      <c r="L2" s="39" t="n"/>
-      <c r="M2" s="39" t="n"/>
-      <c r="N2" s="39" t="n"/>
-      <c r="O2" s="39" t="n"/>
-      <c r="P2" s="39" t="n"/>
-      <c r="Q2" s="39" t="n"/>
+      <c r="L2" s="35" t="n"/>
+      <c r="M2" s="35" t="n"/>
+      <c r="N2" s="35" t="n"/>
+      <c r="O2" s="35" t="n"/>
+      <c r="P2" s="35" t="n"/>
+      <c r="Q2" s="35" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>DEF2</t>
         </is>
       </c>
-      <c r="B3" s="40" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>Coles Lite Reduced Fat Milk | 2L</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="38" t="inlineStr">
         <is>
           <t>Reduced fat milk</t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F3" s="39" t="n"/>
-      <c r="G3" s="39" t="n"/>
-      <c r="H3" s="39" t="n"/>
-      <c r="I3" s="39" t="n"/>
-      <c r="J3" s="39" t="n"/>
-      <c r="K3" s="39" t="n"/>
-      <c r="L3" s="39" t="inlineStr">
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n"/>
+      <c r="I3" s="35" t="n"/>
+      <c r="J3" s="35" t="n"/>
+      <c r="K3" s="35" t="n"/>
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>Low or reduced-fat plain and evaporated milk, and buttermilk is green</t>
         </is>
       </c>
-      <c r="M3" s="39" t="n"/>
-      <c r="N3" s="39" t="n"/>
-      <c r="O3" s="39" t="n"/>
-      <c r="P3" s="39" t="n"/>
-      <c r="Q3" s="39" t="n"/>
+      <c r="M3" s="35" t="n"/>
+      <c r="N3" s="35" t="n"/>
+      <c r="O3" s="35" t="n"/>
+      <c r="P3" s="35" t="n"/>
+      <c r="Q3" s="35" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>DEF3</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Coles Light Ricotta 375g</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Ricotta cheese</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>3.7 g</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>197 mg</t>
         </is>
       </c>
-      <c r="H4" s="39" t="n">
+      <c r="H4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>3.8 g</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>378 mg</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="39" t="inlineStr">
         <is>
           <t>Cheese that is naturally lower in fat (such as ricotta cheese)</t>
         </is>
       </c>
-      <c r="L4" s="39" t="n"/>
-      <c r="M4" s="39" t="n"/>
-      <c r="N4" s="39" t="n"/>
-      <c r="O4" s="39" t="n"/>
-      <c r="P4" s="39" t="n"/>
-      <c r="Q4" s="39" t="n"/>
+      <c r="L4" s="35" t="n"/>
+      <c r="M4" s="35" t="n"/>
+      <c r="N4" s="35" t="n"/>
+      <c r="O4" s="35" t="n"/>
+      <c r="P4" s="35" t="n"/>
+      <c r="Q4" s="35" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>DEF4</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>Coles Regular Soy Milk | 1L</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Soy Milk</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F5" s="39" t="n"/>
-      <c r="G5" s="39" t="n"/>
-      <c r="H5" s="39" t="n"/>
-      <c r="I5" s="39" t="n"/>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="35" t="n"/>
+      <c r="I5" s="35" t="n"/>
+      <c r="J5" s="39" t="inlineStr">
         <is>
           <t>110 mg</t>
         </is>
       </c>
-      <c r="K5" s="39" t="n"/>
-      <c r="L5" s="39" t="n"/>
-      <c r="M5" s="39" t="n"/>
-      <c r="N5" s="41" t="n"/>
-      <c r="O5" s="41" t="inlineStr">
+      <c r="K5" s="35" t="n"/>
+      <c r="L5" s="35" t="n"/>
+      <c r="M5" s="35" t="n"/>
+      <c r="N5" s="37" t="n"/>
+      <c r="O5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">100g per 100ml </t>
         </is>
       </c>
-      <c r="P5" s="39" t="n"/>
-      <c r="Q5" s="39" t="inlineStr">
+      <c r="P5" s="35" t="n"/>
+      <c r="Q5" s="35" t="inlineStr">
         <is>
           <t>Unflavoured calcium-fortified milk alternatives (including soy/rice/almond drink) with at least 100mg of added calcium per 100mL are green</t>
         </is>
@@ -19355,361 +19314,361 @@
       <c r="R5" s="1" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>DEF5</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Farmers Union Protein Yoghurt 900g</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>Protein greek yoghurt</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>0.2 g</t>
         </is>
       </c>
-      <c r="G6" s="39" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>59 mg</t>
         </is>
       </c>
-      <c r="H6" s="39" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>0.0 g</t>
         </is>
       </c>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>4.9 g</t>
         </is>
       </c>
-      <c r="J6" s="41" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">
 269 mg</t>
         </is>
       </c>
-      <c r="K6" s="43" t="inlineStr">
+      <c r="K6" s="39" t="inlineStr">
         <is>
           <t>2g total fat or less per 100g</t>
         </is>
       </c>
-      <c r="L6" s="39" t="n"/>
-      <c r="M6" s="39" t="n"/>
-      <c r="N6" s="39" t="n"/>
-      <c r="O6" s="39" t="n"/>
-      <c r="P6" s="39" t="n"/>
-      <c r="Q6" s="39" t="inlineStr">
+      <c r="L6" s="35" t="n"/>
+      <c r="M6" s="35" t="n"/>
+      <c r="N6" s="35" t="n"/>
+      <c r="O6" s="35" t="n"/>
+      <c r="P6" s="35" t="n"/>
+      <c r="Q6" s="35" t="inlineStr">
         <is>
           <t>Regular-fat varieties are amber._x000D_Choose mostly natural, unsweetened yoghurt or alternatives.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>DEF6</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Coles Free Range Eggs 12 Pack | 700g</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Eggs</t>
         </is>
       </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F7" s="39" t="n"/>
-      <c r="G7" s="39" t="n"/>
-      <c r="H7" s="39" t="n"/>
-      <c r="I7" s="39" t="n"/>
-      <c r="J7" s="39" t="n"/>
-      <c r="K7" s="39" t="inlineStr">
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="35" t="n"/>
+      <c r="J7" s="35" t="n"/>
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">eggs = green </t>
         </is>
       </c>
-      <c r="L7" s="39" t="n"/>
-      <c r="M7" s="39" t="n"/>
-      <c r="N7" s="39" t="n"/>
-      <c r="O7" s="39" t="n"/>
-      <c r="P7" s="39" t="n"/>
-      <c r="Q7" s="39" t="n"/>
+      <c r="L7" s="35" t="n"/>
+      <c r="M7" s="35" t="n"/>
+      <c r="N7" s="35" t="n"/>
+      <c r="O7" s="35" t="n"/>
+      <c r="P7" s="35" t="n"/>
+      <c r="Q7" s="35" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>DEF7</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Bulla Cottage Cheese Original 200g</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Cottage cheese</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F8" s="42" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">
 1.8g</t>
         </is>
       </c>
-      <c r="G8" s="41" t="inlineStr">
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">
 312.0mg</t>
         </is>
       </c>
-      <c r="H8" s="39" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="I8" s="39" t="inlineStr">
+      <c r="I8" s="35" t="inlineStr">
         <is>
           <t>4.2g</t>
         </is>
       </c>
-      <c r="J8" s="39" t="inlineStr">
+      <c r="J8" s="35" t="inlineStr">
         <is>
           <t>106mg</t>
         </is>
       </c>
-      <c r="K8" s="42" t="inlineStr">
+      <c r="K8" s="38" t="inlineStr">
         <is>
           <t>Cheese that is naturally lower in fat (such as cottage cheese)</t>
         </is>
       </c>
-      <c r="L8" s="41" t="n"/>
-      <c r="M8" s="39" t="n"/>
-      <c r="N8" s="39" t="n"/>
-      <c r="O8" s="39" t="n"/>
-      <c r="P8" s="39" t="n"/>
-      <c r="Q8" s="39" t="n"/>
+      <c r="L8" s="37" t="n"/>
+      <c r="M8" s="35" t="n"/>
+      <c r="N8" s="35" t="n"/>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="35" t="n"/>
+      <c r="Q8" s="35" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>DEF8</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Tempo Reduced Fat Cheddar Cheese Block  250g</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Reduced Fat Cheddar Cheese</t>
         </is>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F9" s="39" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">22.4g </t>
         </is>
       </c>
-      <c r="G9" s="39" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">580mg </t>
         </is>
       </c>
-      <c r="H9" s="39" t="inlineStr">
+      <c r="H9" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="I9" s="39" t="inlineStr">
+      <c r="I9" s="35" t="inlineStr">
         <is>
           <t>0.6g</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J9" s="35" t="inlineStr">
         <is>
           <t>790mg</t>
         </is>
       </c>
-      <c r="K9" s="43" t="inlineStr">
+      <c r="K9" s="39" t="inlineStr">
         <is>
           <t>Cheese that is naturally lower in fat (such as reduced fat cheddar cheese)</t>
         </is>
       </c>
-      <c r="L9" s="39" t="n"/>
-      <c r="M9" s="39" t="n"/>
-      <c r="N9" s="39" t="n"/>
-      <c r="O9" s="39" t="n"/>
-      <c r="P9" s="39" t="n"/>
-      <c r="Q9" s="39" t="inlineStr">
+      <c r="L9" s="35" t="n"/>
+      <c r="M9" s="35" t="n"/>
+      <c r="N9" s="35" t="n"/>
+      <c r="O9" s="35" t="n"/>
+      <c r="P9" s="35" t="n"/>
+      <c r="Q9" s="35" t="inlineStr">
         <is>
           <t>Offer these as standard options.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>DEF9</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>On The Menu Fresh Napoli Sauce | 425g</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>Fresh Napoli Sauce</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>0.1 g</t>
         </is>
       </c>
-      <c r="G10" s="43" t="inlineStr">
+      <c r="G10" s="39" t="inlineStr">
         <is>
           <t>274 mg</t>
         </is>
       </c>
-      <c r="H10" s="39" t="inlineStr">
+      <c r="H10" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="I10" s="39" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t>5.9 g</t>
         </is>
       </c>
-      <c r="J10" s="39" t="n"/>
-      <c r="K10" s="43" t="inlineStr">
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="39" t="inlineStr">
         <is>
           <t>2g or less</t>
         </is>
       </c>
-      <c r="L10" s="43" t="inlineStr">
+      <c r="L10" s="39" t="inlineStr">
         <is>
           <t>300mg or less</t>
         </is>
       </c>
-      <c r="M10" s="39" t="n"/>
-      <c r="N10" s="39" t="n"/>
-      <c r="O10" s="39" t="n"/>
-      <c r="P10" s="39" t="n"/>
-      <c r="Q10" s="39" t="n"/>
+      <c r="M10" s="35" t="n"/>
+      <c r="N10" s="35" t="n"/>
+      <c r="O10" s="35" t="n"/>
+      <c r="P10" s="35" t="n"/>
+      <c r="Q10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>DEF10</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Simply Better Plain Firm Tofu | 375g</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Tofu</t>
         </is>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Healthy</t>
         </is>
       </c>
-      <c r="F11" s="39" t="n"/>
-      <c r="G11" s="39" t="n"/>
-      <c r="H11" s="39" t="n"/>
-      <c r="I11" s="39" t="n"/>
-      <c r="J11" s="39" t="n"/>
-      <c r="K11" s="39" t="inlineStr">
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+      <c r="K11" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Plain tofu = green </t>
         </is>
       </c>
-      <c r="L11" s="39" t="n"/>
-      <c r="M11" s="39" t="n"/>
-      <c r="N11" s="39" t="n"/>
-      <c r="O11" s="39" t="n"/>
-      <c r="P11" s="39" t="n"/>
-      <c r="Q11" s="39" t="n"/>
+      <c r="L11" s="35" t="n"/>
+      <c r="M11" s="35" t="n"/>
+      <c r="N11" s="35" t="n"/>
+      <c r="O11" s="35" t="n"/>
+      <c r="P11" s="35" t="n"/>
+      <c r="Q11" s="35" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>DEF11</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -19729,7 +19688,7 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>1.0 g</t>
         </is>
@@ -19739,48 +19698,48 @@
           <t>849 mg</t>
         </is>
       </c>
-      <c r="H12" s="41" t="inlineStr">
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">50g </t>
         </is>
       </c>
-      <c r="I12" s="41" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
         <is>
           <t>429 kJ</t>
         </is>
       </c>
-      <c r="J12" s="41" t="n"/>
-      <c r="K12" s="41" t="inlineStr">
+      <c r="J12" s="37" t="n"/>
+      <c r="K12" s="37" t="inlineStr">
         <is>
           <t>3g or less</t>
         </is>
       </c>
-      <c r="L12" s="41" t="inlineStr">
+      <c r="L12" s="37" t="inlineStr">
         <is>
           <t>750mg or less</t>
         </is>
       </c>
-      <c r="M12" s="41" t="n"/>
-      <c r="N12" s="41" t="inlineStr">
+      <c r="M12" s="37" t="n"/>
+      <c r="N12" s="37" t="inlineStr">
         <is>
           <t>serving size 50g or less</t>
         </is>
       </c>
-      <c r="O12" s="41" t="inlineStr">
+      <c r="O12" s="37" t="inlineStr">
         <is>
           <t>energy 1,000kJ or less</t>
         </is>
       </c>
-      <c r="P12" s="39" t="n"/>
-      <c r="Q12" s="39" t="n"/>
+      <c r="P12" s="35" t="n"/>
+      <c r="Q12" s="35" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>DEF12</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -19801,22 +19760,22 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>9.7 g</t>
         </is>
       </c>
-      <c r="G13" s="41" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>15 mg</t>
         </is>
       </c>
-      <c r="H13" s="39" t="inlineStr">
+      <c r="H13" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="I13" s="39" t="inlineStr">
+      <c r="I13" s="35" t="inlineStr">
         <is>
           <t>2 g</t>
         </is>
@@ -19826,25 +19785,25 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="K13" s="41" t="n"/>
-      <c r="L13" s="39" t="n"/>
-      <c r="M13" s="39" t="n"/>
-      <c r="N13" s="39" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="35" t="n"/>
+      <c r="M13" s="35" t="n"/>
+      <c r="N13" s="35" t="n"/>
       <c r="O13" s="19" t="inlineStr">
         <is>
           <t>Coconut-based yoghurts are red.</t>
         </is>
       </c>
-      <c r="P13" s="39" t="n"/>
-      <c r="Q13" s="39" t="n"/>
+      <c r="P13" s="35" t="n"/>
+      <c r="Q13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>DEF13</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -19874,7 +19833,7 @@
           <t>1420 mg</t>
         </is>
       </c>
-      <c r="H14" s="39" t="inlineStr">
+      <c r="H14" s="35" t="inlineStr">
         <is>
           <t>40 g</t>
         </is>
@@ -19884,22 +19843,22 @@
           <t>1680 kJ</t>
         </is>
       </c>
-      <c r="J14" s="39" t="n"/>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
-      <c r="M14" s="39" t="n"/>
-      <c r="N14" s="39" t="n"/>
-      <c r="O14" s="39" t="n"/>
-      <c r="P14" s="39" t="n"/>
-      <c r="Q14" s="39" t="n"/>
+      <c r="J14" s="35" t="n"/>
+      <c r="K14" s="35" t="n"/>
+      <c r="L14" s="35" t="n"/>
+      <c r="M14" s="35" t="n"/>
+      <c r="N14" s="35" t="n"/>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>DEF14</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -19919,7 +19878,7 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="35" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -19930,27 +19889,27 @@
       <c r="H15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="39" t="inlineStr">
+      <c r="I15" s="35" t="inlineStr">
         <is>
           <t>395 kJ</t>
         </is>
       </c>
-      <c r="J15" s="39" t="n"/>
-      <c r="K15" s="39" t="n"/>
-      <c r="L15" s="39" t="n"/>
-      <c r="M15" s="39" t="n"/>
-      <c r="N15" s="39" t="n"/>
-      <c r="O15" s="39" t="n"/>
-      <c r="P15" s="39" t="n"/>
-      <c r="Q15" s="39" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="35" t="n"/>
+      <c r="M15" s="35" t="n"/>
+      <c r="N15" s="35" t="n"/>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>DEF15</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -19971,7 +19930,7 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F16" s="39" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>1.2 g</t>
         </is>
@@ -19981,28 +19940,28 @@
           <t>925 mg</t>
         </is>
       </c>
-      <c r="H16" s="39" t="n"/>
-      <c r="I16" s="39" t="inlineStr">
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="inlineStr">
         <is>
           <t>477 kJ</t>
         </is>
       </c>
-      <c r="J16" s="39" t="n"/>
-      <c r="K16" s="39" t="n"/>
-      <c r="L16" s="39" t="n"/>
-      <c r="M16" s="39" t="n"/>
-      <c r="N16" s="39" t="n"/>
-      <c r="O16" s="39" t="n"/>
-      <c r="P16" s="39" t="n"/>
-      <c r="Q16" s="39" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="35" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>DEF16</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20032,40 +19991,40 @@
           <t>416 mg</t>
         </is>
       </c>
-      <c r="H17" s="39" t="inlineStr">
+      <c r="H17" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="I17" s="39" t="inlineStr">
+      <c r="I17" s="35" t="inlineStr">
         <is>
           <t>2.4 g</t>
         </is>
       </c>
-      <c r="J17" s="39" t="n"/>
+      <c r="J17" s="35" t="n"/>
       <c r="K17" s="19" t="inlineStr">
         <is>
           <t>&gt;5 g</t>
         </is>
       </c>
-      <c r="L17" s="39" t="inlineStr">
+      <c r="L17" s="35" t="inlineStr">
         <is>
           <t>&gt;700mg</t>
         </is>
       </c>
-      <c r="M17" s="39" t="n"/>
-      <c r="N17" s="39" t="n"/>
-      <c r="O17" s="39" t="n"/>
-      <c r="P17" s="39" t="n"/>
-      <c r="Q17" s="39" t="n"/>
+      <c r="M17" s="35" t="n"/>
+      <c r="N17" s="35" t="n"/>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>DEF17</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20095,28 +20054,28 @@
           <t>1000 mg</t>
         </is>
       </c>
-      <c r="H18" s="39" t="n"/>
+      <c r="H18" s="35" t="n"/>
       <c r="I18" s="19" t="inlineStr">
         <is>
           <t>1030 kJ</t>
         </is>
       </c>
-      <c r="J18" s="39" t="n"/>
-      <c r="K18" s="39" t="n"/>
-      <c r="L18" s="39" t="n"/>
-      <c r="M18" s="39" t="n"/>
-      <c r="N18" s="39" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="39" t="n"/>
-      <c r="Q18" s="39" t="n"/>
+      <c r="J18" s="35" t="n"/>
+      <c r="K18" s="35" t="n"/>
+      <c r="L18" s="35" t="n"/>
+      <c r="M18" s="35" t="n"/>
+      <c r="N18" s="35" t="n"/>
+      <c r="O18" s="35" t="n"/>
+      <c r="P18" s="35" t="n"/>
+      <c r="Q18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>DEF18</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20136,7 +20095,7 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F19" s="39" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>1.8 g</t>
         </is>
@@ -20149,27 +20108,27 @@
       <c r="H19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="39" t="inlineStr">
+      <c r="I19" s="35" t="inlineStr">
         <is>
           <t>536 kJ</t>
         </is>
       </c>
-      <c r="J19" s="39" t="n"/>
-      <c r="K19" s="39" t="n"/>
-      <c r="L19" s="39" t="n"/>
-      <c r="M19" s="39" t="n"/>
-      <c r="N19" s="39" t="n"/>
-      <c r="O19" s="39" t="n"/>
-      <c r="P19" s="39" t="n"/>
-      <c r="Q19" s="39" t="n"/>
+      <c r="J19" s="35" t="n"/>
+      <c r="K19" s="35" t="n"/>
+      <c r="L19" s="35" t="n"/>
+      <c r="M19" s="35" t="n"/>
+      <c r="N19" s="35" t="n"/>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>DEF19</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20189,13 +20148,13 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F20" s="39" t="n">
+      <c r="F20" s="35" t="n">
         <v>7.6</v>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="35" t="n">
         <v>39.5</v>
       </c>
-      <c r="H20" s="39" t="inlineStr">
+      <c r="H20" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
@@ -20203,34 +20162,34 @@
       <c r="I20" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="J20" s="39" t="inlineStr">
+      <c r="J20" s="35" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="K20" s="39" t="n"/>
-      <c r="L20" s="39" t="n"/>
-      <c r="M20" s="39" t="n"/>
+      <c r="K20" s="35" t="n"/>
+      <c r="L20" s="35" t="n"/>
+      <c r="M20" s="35" t="n"/>
       <c r="N20" s="19" t="inlineStr">
         <is>
           <t>no added chocolate</t>
         </is>
       </c>
-      <c r="O20" s="39" t="n"/>
-      <c r="P20" s="39" t="n"/>
-      <c r="Q20" s="39" t="inlineStr">
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="35" t="n"/>
+      <c r="Q20" s="35" t="inlineStr">
         <is>
           <t>Commercial yoghurt products with added ingredients are red if they contain confectionery such as chocolate chips, sweet biscuits, or sweet toppings and sauces such as caramel.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>DEF20</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20261,48 +20220,48 @@
           <t>768 mg</t>
         </is>
       </c>
-      <c r="H21" s="39" t="n"/>
-      <c r="I21" s="39" t="inlineStr">
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="inlineStr">
         <is>
           <t>1260 kJ</t>
         </is>
       </c>
-      <c r="J21" s="39" t="inlineStr">
+      <c r="J21" s="35" t="inlineStr">
         <is>
           <t>2g or less</t>
         </is>
       </c>
-      <c r="K21" s="39" t="inlineStr">
+      <c r="K21" s="35" t="inlineStr">
         <is>
           <t>300mg or less</t>
         </is>
       </c>
-      <c r="L21" s="39" t="inlineStr">
+      <c r="L21" s="35" t="inlineStr">
         <is>
           <t>3g or more</t>
         </is>
       </c>
-      <c r="M21" s="39" t="inlineStr">
+      <c r="M21" s="35" t="inlineStr">
         <is>
           <t>2,500kJ or less</t>
         </is>
       </c>
-      <c r="N21" s="39" t="n"/>
-      <c r="O21" s="39" t="inlineStr">
+      <c r="N21" s="35" t="n"/>
+      <c r="O21" s="35" t="inlineStr">
         <is>
           <t>Processed meats are high in saturated fat and/or sodium (salt) and are amber or red.</t>
         </is>
       </c>
-      <c r="P21" s="39" t="n"/>
-      <c r="Q21" s="39" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
     </row>
     <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>DEF21</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20332,36 +20291,36 @@
           <t xml:space="preserve">939mg </t>
         </is>
       </c>
-      <c r="H22" s="39" t="inlineStr">
+      <c r="H22" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">NR </t>
         </is>
       </c>
-      <c r="I22" s="39" t="inlineStr">
+      <c r="I22" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">620kj </t>
         </is>
       </c>
-      <c r="J22" s="39" t="n"/>
-      <c r="K22" s="39" t="n"/>
-      <c r="L22" s="39" t="n"/>
-      <c r="M22" s="39" t="n"/>
-      <c r="N22" s="41" t="inlineStr">
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="35" t="n"/>
+      <c r="M22" s="35" t="n"/>
+      <c r="N22" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Processed chicken </t>
         </is>
       </c>
-      <c r="O22" s="41" t="n"/>
-      <c r="P22" s="39" t="n"/>
-      <c r="Q22" s="39" t="n"/>
+      <c r="O22" s="37" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>DEF22</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20391,28 +20350,28 @@
           <t>1027 mg</t>
         </is>
       </c>
-      <c r="H23" s="39" t="n"/>
-      <c r="I23" s="39" t="inlineStr">
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="35" t="inlineStr">
         <is>
           <t>1060 kJ</t>
         </is>
       </c>
-      <c r="J23" s="39" t="n"/>
-      <c r="K23" s="39" t="n"/>
-      <c r="L23" s="39" t="n"/>
-      <c r="M23" s="39" t="n"/>
-      <c r="N23" s="39" t="n"/>
-      <c r="O23" s="39" t="n"/>
-      <c r="P23" s="39" t="n"/>
-      <c r="Q23" s="39" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="35" t="n"/>
+      <c r="N23" s="35" t="n"/>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>DEF23</t>
         </is>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20445,43 +20404,43 @@
       <c r="H24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="39" t="inlineStr">
+      <c r="I24" s="35" t="inlineStr">
         <is>
           <t>1120 kJ</t>
         </is>
       </c>
-      <c r="J24" s="39" t="inlineStr">
+      <c r="J24" s="35" t="inlineStr">
         <is>
           <t>2g or less</t>
         </is>
       </c>
-      <c r="K24" s="39" t="inlineStr">
+      <c r="K24" s="35" t="inlineStr">
         <is>
           <t>300mg or less</t>
         </is>
       </c>
-      <c r="L24" s="39" t="inlineStr">
+      <c r="L24" s="35" t="inlineStr">
         <is>
           <t>3g or more</t>
         </is>
       </c>
-      <c r="M24" s="39" t="inlineStr">
+      <c r="M24" s="35" t="inlineStr">
         <is>
           <t>2,500kJ or less</t>
         </is>
       </c>
-      <c r="N24" s="39" t="n"/>
-      <c r="O24" s="39" t="n"/>
-      <c r="P24" s="39" t="n"/>
-      <c r="Q24" s="39" t="n"/>
+      <c r="N24" s="35" t="n"/>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>DEF24</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20501,7 +20460,7 @@
           <t>UnHealthy</t>
         </is>
       </c>
-      <c r="F25" s="39" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr">
         <is>
           <t>1.6 g</t>
         </is>
@@ -20511,28 +20470,28 @@
           <t>931 mg</t>
         </is>
       </c>
-      <c r="H25" s="39" t="n"/>
-      <c r="I25" s="39" t="inlineStr">
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="35" t="inlineStr">
         <is>
           <t>571 kJ</t>
         </is>
       </c>
-      <c r="J25" s="39" t="n"/>
-      <c r="K25" s="41" t="n"/>
-      <c r="L25" s="41" t="n"/>
-      <c r="M25" s="39" t="n"/>
-      <c r="N25" s="39" t="n"/>
-      <c r="O25" s="39" t="n"/>
-      <c r="P25" s="39" t="n"/>
-      <c r="Q25" s="39" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="37" t="n"/>
+      <c r="L25" s="37" t="n"/>
+      <c r="M25" s="35" t="n"/>
+      <c r="N25" s="35" t="n"/>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>DEF25</t>
         </is>
       </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20562,9 +20521,9 @@
           <t>Energy per serving 733 kJ</t>
         </is>
       </c>
-      <c r="H26" s="39" t="n"/>
-      <c r="I26" s="39" t="n"/>
-      <c r="J26" s="39" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="35" t="n"/>
       <c r="K26" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3g or less </t>
@@ -20575,23 +20534,23 @@
           <t>600kJ or less</t>
         </is>
       </c>
-      <c r="M26" s="39" t="n"/>
-      <c r="N26" s="39" t="n"/>
-      <c r="O26" s="39" t="n"/>
-      <c r="P26" s="39" t="n"/>
-      <c r="Q26" s="39" t="inlineStr">
+      <c r="M26" s="35" t="n"/>
+      <c r="N26" s="35" t="n"/>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Choclate pudding </t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>DEF26</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20621,28 +20580,28 @@
           <t>1700 mg</t>
         </is>
       </c>
-      <c r="H27" s="39" t="n"/>
-      <c r="I27" s="39" t="inlineStr">
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="35" t="inlineStr">
         <is>
           <t>1270 kJ</t>
         </is>
       </c>
-      <c r="J27" s="39" t="n"/>
-      <c r="K27" s="39" t="n"/>
-      <c r="L27" s="39" t="n"/>
-      <c r="M27" s="39" t="n"/>
-      <c r="N27" s="39" t="n"/>
-      <c r="O27" s="39" t="n"/>
-      <c r="P27" s="39" t="n"/>
-      <c r="Q27" s="39" t="n"/>
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="35" t="n"/>
+      <c r="L27" s="35" t="n"/>
+      <c r="M27" s="35" t="n"/>
+      <c r="N27" s="35" t="n"/>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
     </row>
     <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>DEF27</t>
         </is>
       </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20673,33 +20632,33 @@
 773.0mg</t>
         </is>
       </c>
-      <c r="H28" s="39" t="n"/>
+      <c r="H28" s="35" t="n"/>
       <c r="I28" s="18" t="inlineStr">
         <is>
           <t>Per serving350.0kJ
 701.0kJ</t>
         </is>
       </c>
-      <c r="J28" s="39" t="n"/>
-      <c r="K28" s="39" t="n"/>
-      <c r="L28" s="39" t="n"/>
-      <c r="M28" s="39" t="n"/>
-      <c r="N28" s="39" t="inlineStr">
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="35" t="n"/>
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="35" t="n"/>
+      <c r="N28" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Fritz </t>
         </is>
       </c>
-      <c r="O28" s="39" t="n"/>
-      <c r="P28" s="39" t="n"/>
-      <c r="Q28" s="39" t="n"/>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="35" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>DEF28</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>Dairy Eggs Fridge</t>
         </is>
@@ -20730,20 +20689,20 @@
           <t>1000 mg</t>
         </is>
       </c>
-      <c r="H29" s="39" t="n"/>
-      <c r="I29" s="41" t="inlineStr">
+      <c r="H29" s="35" t="n"/>
+      <c r="I29" s="37" t="inlineStr">
         <is>
           <t>635 kJ</t>
         </is>
       </c>
-      <c r="J29" s="39" t="n"/>
-      <c r="K29" s="39" t="n"/>
-      <c r="L29" s="39" t="n"/>
-      <c r="M29" s="39" t="n"/>
-      <c r="N29" s="39" t="n"/>
-      <c r="O29" s="39" t="n"/>
-      <c r="P29" s="39" t="n"/>
-      <c r="Q29" s="39" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="35" t="n"/>
+      <c r="L29" s="35" t="n"/>
+      <c r="M29" s="35" t="n"/>
+      <c r="N29" s="35" t="n"/>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Combined Justification 8.05.2026.xlsx
+++ b/Combined Justification 8.05.2026.xlsx
@@ -8710,11 +8710,13 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8737,6 +8739,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8759,6 +8764,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8781,6 +8789,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8808,6 +8818,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8830,6 +8843,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8889,6 +8905,7 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8921,6 +8938,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8943,6 +8963,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8965,6 +8988,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8987,6 +9013,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9009,6 +9038,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9031,6 +9063,13 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9053,16 +9092,13 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9085,6 +9121,13 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9107,6 +9150,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9129,6 +9175,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9151,6 +9200,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9173,6 +9225,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9195,6 +9250,13 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9217,6 +9279,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9239,6 +9304,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9303,6 +9371,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9330,6 +9399,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9352,6 +9424,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9374,6 +9449,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9396,6 +9474,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9418,6 +9499,7 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9450,6 +9532,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9472,6 +9557,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9494,6 +9582,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9516,6 +9607,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9538,6 +9632,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9560,6 +9657,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9582,6 +9682,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9604,6 +9707,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9631,6 +9736,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9653,6 +9761,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9675,6 +9786,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9697,6 +9811,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9719,6 +9836,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9741,6 +9861,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9763,6 +9886,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9785,6 +9911,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9844,6 +9973,17 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9866,6 +10006,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9888,6 +10031,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9910,6 +10056,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9932,6 +10081,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9954,6 +10106,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9976,6 +10131,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9998,6 +10156,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10012,7 +10173,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Energy Drink</t>
+          <t>Energy drink</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -10020,6 +10181,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -10042,6 +10206,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10064,6 +10231,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10086,6 +10256,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10108,6 +10280,10 @@
           <t>Protein water citrus</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10130,6 +10306,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10144,7 +10323,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wholegrain rice crackers</t>
+          <t>Wholegrain rice cracker</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10152,6 +10331,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10166,7 +10348,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Multigrain crispbread crackers</t>
+          <t>Multigrain crispbread cracker</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10174,6 +10356,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10188,7 +10373,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mini rice crisps milk chocolate</t>
+          <t>Rice crisps milk chocolate</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10196,6 +10381,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10218,6 +10406,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10245,6 +10435,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10259,7 +10452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jelly beans</t>
+          <t>Jelly bean</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10267,6 +10460,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10289,6 +10485,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10303,7 +10502,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Marshmallows</t>
+          <t>Marshmallow</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10311,6 +10510,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10333,11 +10535,13 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10360,6 +10564,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10382,6 +10589,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10404,6 +10614,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10418,7 +10631,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plain crackers</t>
+          <t>Plain cracker</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10426,6 +10639,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10440,7 +10656,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pretzels</t>
+          <t>Pretzel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10448,6 +10664,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10462,7 +10681,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Original potato chips</t>
+          <t>Original potato chip</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10470,6 +10689,7 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10502,6 +10722,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10524,6 +10747,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10538,7 +10764,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cheese corn chips</t>
+          <t>Cheese corn chip</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10546,6 +10772,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10560,7 +10789,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Choclate chip cookies</t>
+          <t>Choclate chip cookie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10568,6 +10797,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10590,6 +10822,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10604,7 +10839,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chocolate coated biscuits</t>
+          <t>Chocolate coated biscuit</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10612,6 +10847,7 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10636,7 +10872,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chocolate cream wafers</t>
+          <t>Chocolate cream wafer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10644,11 +10880,9 @@
           <t>unhealthy</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10671,11 +10905,13 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10690,7 +10926,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rice bubbles snack bars</t>
+          <t>Rice bubbles snack bar</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10698,6 +10934,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10712,7 +10951,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Flavoured rainbow Sticks</t>
+          <t>Flavoured rainbow stick</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10720,6 +10959,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10742,6 +10984,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10769,6 +11014,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10796,6 +11042,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10810,7 +11059,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>Grape</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -10818,6 +11067,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10840,6 +11092,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10862,6 +11117,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10884,6 +11142,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10898,7 +11159,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>pears</t>
+          <t>Pear</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -10906,6 +11167,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10920,7 +11184,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>Pineapple</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10928,6 +11192,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10955,6 +11222,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10969,7 +11238,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bannanas</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11006,7 +11275,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -11014,6 +11283,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11036,6 +11308,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11050,7 +11325,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canned peaches</t>
+          <t>Canned peache</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -11058,6 +11333,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11080,6 +11358,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11102,6 +11383,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11124,6 +11408,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11138,7 +11425,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Banana Chips</t>
+          <t>Banana Chip</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11146,6 +11433,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11168,6 +11458,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11190,6 +11483,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11212,6 +11508,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11234,6 +11533,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11256,6 +11558,13 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11278,6 +11587,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11300,6 +11612,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11314,7 +11629,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pork sizzle steaks</t>
+          <t>Pork sizzle steak</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -11322,6 +11637,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11344,6 +11662,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11366,6 +11687,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11380,7 +11704,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicken breast fillets</t>
+          <t>Chicken breast fillet</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -11425,6 +11749,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11447,6 +11774,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11469,6 +11799,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11491,6 +11824,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11505,7 +11841,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tuna steaks</t>
+          <t>Tuna steak</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -11513,6 +11849,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11527,7 +11866,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thin Bbq sausages</t>
+          <t>Thin Bbq sausage</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -11535,6 +11874,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11554,7 +11895,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Beef sausages</t>
+          <t>Beef sausage</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -11562,6 +11903,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11576,7 +11920,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Beef burgers patties</t>
+          <t>Beef burgers pattie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11584,6 +11928,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11603,7 +11949,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lamb burgers</t>
+          <t>Lamb burger</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11611,6 +11957,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11625,7 +11974,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Beef Bbq burgers</t>
+          <t>Beef Bbq burger</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11633,6 +11982,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11647,7 +11999,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kransky bites</t>
+          <t>Kransky bite</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11655,6 +12007,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11677,6 +12032,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11699,6 +12057,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11721,6 +12082,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11748,6 +12111,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11770,11 +12136,7 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11807,6 +12169,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11829,6 +12194,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11843,7 +12211,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Frozen Broccoli</t>
+          <t>Frozen broccoli</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11856,6 +12224,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11870,7 +12240,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Frozen Vegetable Mix</t>
+          <t>Frozen vegetable mix</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11878,6 +12248,13 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11892,7 +12269,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Frozen Cauliflower</t>
+          <t>Frozen cauliflower</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11900,6 +12277,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11922,6 +12302,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11936,7 +12319,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Frozen Beans</t>
+          <t>Frozen beans</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11944,6 +12327,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11958,7 +12344,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chinese Stir Fry Mix Veg</t>
+          <t>Chinese stir fry mix veg</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11966,6 +12352,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11980,7 +12369,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Frozen Carrots</t>
+          <t>Frozen carrots</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11988,6 +12377,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12002,7 +12394,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Flavoured Iceblocks</t>
+          <t>Flavoured iceblocks</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12010,11 +12402,13 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12037,6 +12431,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12059,11 +12456,13 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12086,6 +12485,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12108,6 +12510,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12122,7 +12527,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chocolate Bavarian</t>
+          <t>Chocolate bavarian</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12130,6 +12535,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12152,6 +12560,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12174,6 +12585,17 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12188,7 +12610,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Meatlovers Pizza</t>
+          <t>Meatlovers pizza</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -12196,6 +12618,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12218,6 +12643,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12240,6 +12668,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12262,6 +12693,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12276,7 +12710,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cheese &amp; Bacon Pizza</t>
+          <t>Cheese &amp; bacon pizza</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -12284,6 +12718,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12298,7 +12735,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hawaiin Pizza</t>
+          <t>Hawaiin pizza</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -12335,7 +12772,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Puff Pastry Sheets</t>
+          <t>Puff pastry sheet</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -12343,6 +12780,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12365,6 +12805,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12379,7 +12822,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Beef Curry Puff</t>
+          <t>Beef curry puff</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -12387,6 +12830,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12401,7 +12847,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Quiche Cheese &amp; Bacon</t>
+          <t>Quiche cheese &amp; bacon</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -12409,6 +12855,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12423,7 +12872,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dim Sim</t>
+          <t>Dim sim</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -12431,6 +12880,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12458,6 +12910,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12480,6 +12934,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12502,6 +12959,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12524,6 +12984,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12546,6 +13009,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12560,7 +13026,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tortillas</t>
+          <t>Tortilla</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12568,6 +13034,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12590,6 +13059,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12612,6 +13084,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12639,6 +13114,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12661,6 +13138,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12675,7 +13155,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Glass noodles</t>
+          <t>Glass noodle</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12683,6 +13163,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12705,6 +13188,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12727,6 +13213,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12749,6 +13238,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12763,7 +13255,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chick peas</t>
+          <t>Chickpeas</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -12771,6 +13263,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12793,6 +13288,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12815,6 +13313,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12837,6 +13338,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12859,6 +13363,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12881,6 +13388,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12903,16 +13413,9 @@
           <t>healthy</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12935,6 +13438,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12949,7 +13455,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Unsalted mixed nuts</t>
+          <t>Unsalted mixed nut</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -12957,6 +13463,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12971,7 +13480,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Unsalted cashews</t>
+          <t>Unsalted cashew</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -12979,6 +13488,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13006,6 +13518,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13028,6 +13542,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13050,6 +13567,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13072,6 +13592,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13086,7 +13609,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Pumpkin seeds</t>
+          <t>Pumpkin seed</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13094,6 +13617,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13108,7 +13634,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Black chia seeds</t>
+          <t>Black chia seed</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13116,6 +13642,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13130,7 +13659,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sunflower seeds</t>
+          <t>Sunflower seed</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -13138,6 +13667,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13152,7 +13684,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Walnuts</t>
+          <t>Walnut</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13160,6 +13692,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13174,7 +13709,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Almonds</t>
+          <t>Almond</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -13182,6 +13717,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13204,6 +13742,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13226,6 +13767,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13248,6 +13792,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13270,6 +13817,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13297,16 +13847,8 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13329,6 +13871,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13351,6 +13896,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13373,6 +13921,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13395,6 +13946,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13417,6 +13971,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13444,6 +14000,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13471,6 +14029,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13493,6 +14054,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13515,6 +14079,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13537,6 +14104,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13559,6 +14129,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13581,6 +14154,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13603,6 +14179,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13625,6 +14204,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13647,6 +14229,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13679,6 +14264,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13701,6 +14287,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13723,6 +14312,7 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13755,6 +14345,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13782,6 +14374,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13804,6 +14399,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13826,6 +14424,8 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13853,6 +14453,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13875,6 +14478,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13897,6 +14503,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13919,6 +14528,9 @@
           <t>unhealthy</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13941,6 +14553,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13973,6 +14588,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13995,6 +14611,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14009,7 +14628,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>tomatoes</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -14027,6 +14646,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14049,6 +14669,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14081,6 +14704,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14113,6 +14737,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14135,6 +14760,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14157,6 +14785,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14184,6 +14815,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14206,6 +14839,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14228,6 +14864,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14250,6 +14889,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14277,6 +14919,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14299,6 +14943,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14321,6 +14968,9 @@
           <t>healthy</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14353,6 +15003,7 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16021,7 +16672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="B1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -16167,7 +16818,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
@@ -16371,7 +17021,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
@@ -16470,7 +17119,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
@@ -16681,7 +17329,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
@@ -16829,7 +17476,6 @@
         </is>
       </c>
     </row>
-    <row r="119"/>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
@@ -16991,7 +17637,6 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
@@ -17307,7 +17952,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
@@ -17455,7 +18099,6 @@
         </is>
       </c>
     </row>
-    <row r="211"/>
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
@@ -17659,7 +18302,6 @@
         </is>
       </c>
     </row>
-    <row r="241"/>
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>

--- a/Combined Justification 8.05.2026.xlsx
+++ b/Combined Justification 8.05.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyApps\ShoppingCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B655E30F-A50E-4C7B-8676-168B637D687E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BFC6BF-CBE8-4BE6-B75C-9B9281E57316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="897" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="1620">
   <si>
     <t>Item ID</t>
   </si>
@@ -2080,6 +2080,9 @@
     <t xml:space="preserve">Spaghetti </t>
   </si>
   <si>
+    <t xml:space="preserve">free range eggs </t>
+  </si>
+  <si>
     <t>Original potato chips</t>
   </si>
   <si>
@@ -2783,9 +2786,6 @@
   </si>
   <si>
     <t>FRZ12</t>
-  </si>
-  <si>
-    <t>Frozen Dessert Cones - Brownie</t>
   </si>
   <si>
     <t>FRZ13</t>
@@ -5071,9 +5071,6 @@
   </si>
   <si>
     <t>Coles Fresh Celery Sticks Prepacked | 300g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eggs </t>
   </si>
 </sst>
 </file>
@@ -6276,10 +6273,10 @@
     </row>
     <row r="2" spans="1:15" ht="60" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1217</v>
@@ -6317,10 +6314,10 @@
     </row>
     <row r="3" spans="1:15" ht="60" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>810</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>1224</v>
@@ -6360,10 +6357,10 @@
     </row>
     <row r="4" spans="1:15" ht="45" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>1232</v>
@@ -6401,10 +6398,10 @@
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>1235</v>
@@ -6444,10 +6441,10 @@
     </row>
     <row r="6" spans="1:15" ht="45" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>1239</v>
@@ -6476,10 +6473,10 @@
     </row>
     <row r="7" spans="1:15" ht="30" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>1242</v>
@@ -6511,10 +6508,10 @@
     </row>
     <row r="8" spans="1:15" ht="30" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>1244</v>
@@ -6546,10 +6543,10 @@
     </row>
     <row r="9" spans="1:15" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>1247</v>
@@ -6581,10 +6578,10 @@
     </row>
     <row r="10" spans="1:15" ht="30" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>1249</v>
@@ -6616,10 +6613,10 @@
     </row>
     <row r="11" spans="1:15" ht="30" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>1252</v>
@@ -6655,10 +6652,10 @@
     </row>
     <row r="12" spans="1:15" ht="30" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>1255</v>
@@ -6692,10 +6689,10 @@
     </row>
     <row r="13" spans="1:15" ht="30" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>1257</v>
@@ -6727,10 +6724,10 @@
     </row>
     <row r="14" spans="1:15" ht="45" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>1259</v>
@@ -6764,10 +6761,10 @@
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>1262</v>
@@ -6797,10 +6794,10 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>1267</v>
@@ -6830,16 +6827,16 @@
     </row>
     <row r="17" spans="1:15" ht="30" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>1271</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>77</v>
@@ -6861,10 +6858,10 @@
     </row>
     <row r="18" spans="1:15" ht="30" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>1274</v>
@@ -6888,10 +6885,10 @@
     </row>
     <row r="19" spans="1:15" ht="30" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>1275</v>
@@ -6915,10 +6912,10 @@
     </row>
     <row r="20" spans="1:15" ht="30" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>1277</v>
@@ -6948,10 +6945,10 @@
     </row>
     <row r="21" spans="1:15" ht="30" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>1282</v>
@@ -6985,10 +6982,10 @@
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>1287</v>
@@ -7020,10 +7017,10 @@
     </row>
     <row r="23" spans="1:15" ht="30" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>1288</v>
@@ -7057,10 +7054,10 @@
     </row>
     <row r="24" spans="1:15" ht="30" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>1290</v>
@@ -7092,10 +7089,10 @@
     </row>
     <row r="25" spans="1:15" ht="60" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>1293</v>
@@ -7131,10 +7128,10 @@
     </row>
     <row r="26" spans="1:15" ht="30" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>1296</v>
@@ -7168,10 +7165,10 @@
     </row>
     <row r="27" spans="1:15" ht="30" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>1298</v>
@@ -7205,10 +7202,10 @@
     </row>
     <row r="28" spans="1:15" ht="30" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>1301</v>
@@ -7240,10 +7237,10 @@
     </row>
     <row r="29" spans="1:15" ht="30" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>1303</v>
@@ -7296,7 +7293,7 @@
     </row>
     <row r="32" spans="1:15">
       <c r="C32" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O32" t="s">
         <v>1306</v>
@@ -7364,10 +7361,10 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>456</v>
@@ -7384,10 +7381,10 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B3" t="s">
         <v>840</v>
-      </c>
-      <c r="B3" t="s">
-        <v>839</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>1309</v>
@@ -7404,10 +7401,10 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>466</v>
@@ -7424,10 +7421,10 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B5" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>1310</v>
@@ -7444,13 +7441,13 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D6" t="s">
         <v>457</v>
@@ -7464,10 +7461,10 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>1311</v>
@@ -7484,10 +7481,10 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B8" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>1312</v>
@@ -7504,10 +7501,10 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B9" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>472</v>
@@ -7524,10 +7521,10 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>1313</v>
@@ -7544,10 +7541,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B11" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>1314</v>
@@ -7564,10 +7561,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B12" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>468</v>
@@ -7584,10 +7581,10 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B13" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>1315</v>
@@ -7604,10 +7601,10 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B14" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>1316</v>
@@ -7624,10 +7621,10 @@
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
       <c r="A15" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B15" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>1317</v>
@@ -7644,10 +7641,10 @@
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1">
       <c r="A16" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B16" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>1319</v>
@@ -7664,10 +7661,10 @@
     </row>
     <row r="17" spans="1:13" ht="30" customHeight="1">
       <c r="A17" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B17" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>1320</v>
@@ -7687,10 +7684,10 @@
     </row>
     <row r="18" spans="1:13" ht="30" customHeight="1">
       <c r="A18" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B18" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>1323</v>
@@ -7710,10 +7707,10 @@
     </row>
     <row r="19" spans="1:13" ht="30" customHeight="1">
       <c r="A19" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B19" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>1325</v>
@@ -7730,10 +7727,10 @@
     </row>
     <row r="20" spans="1:13" ht="45" customHeight="1">
       <c r="A20" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B20" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>1327</v>
@@ -7750,10 +7747,10 @@
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1">
       <c r="A21" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B21" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>1329</v>
@@ -8691,10 +8688,10 @@
     </row>
     <row r="2" spans="1:16" ht="45" customHeight="1">
       <c r="A2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1332</v>
@@ -8713,10 +8710,10 @@
     </row>
     <row r="3" spans="1:16" ht="45" customHeight="1">
       <c r="A3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B3" t="s">
         <v>867</v>
-      </c>
-      <c r="B3" t="s">
-        <v>866</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>1334</v>
@@ -8735,10 +8732,10 @@
     </row>
     <row r="4" spans="1:16" ht="45" customHeight="1">
       <c r="A4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>1335</v>
@@ -8757,10 +8754,10 @@
     </row>
     <row r="5" spans="1:16" ht="29.25" customHeight="1">
       <c r="A5" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B5" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1336</v>
@@ -8777,10 +8774,10 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B6" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>1339</v>
@@ -8794,10 +8791,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B7" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>1341</v>
@@ -8811,10 +8808,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B8" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>1343</v>
@@ -8828,10 +8825,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B9" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>1344</v>
@@ -8845,10 +8842,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B10" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>1346</v>
@@ -8862,10 +8859,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B11" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>1348</v>
@@ -8879,10 +8876,10 @@
     </row>
     <row r="12" spans="1:16" ht="45" customHeight="1">
       <c r="A12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B12" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>1350</v>
@@ -8902,10 +8899,10 @@
     </row>
     <row r="13" spans="1:16" ht="90" customHeight="1">
       <c r="A13" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>1354</v>
@@ -8929,7 +8926,7 @@
         <v>879</v>
       </c>
       <c r="B14" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>1357</v>
@@ -8962,7 +8959,7 @@
         <v>880</v>
       </c>
       <c r="B15" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>1362</v>
@@ -8995,7 +8992,7 @@
         <v>881</v>
       </c>
       <c r="B16" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>1366</v>
@@ -9027,7 +9024,7 @@
         <v>882</v>
       </c>
       <c r="B17" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>1370</v>
@@ -9055,7 +9052,7 @@
         <v>883</v>
       </c>
       <c r="B18" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>1374</v>
@@ -9083,7 +9080,7 @@
         <v>884</v>
       </c>
       <c r="B19" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>1378</v>
@@ -9111,7 +9108,7 @@
         <v>885</v>
       </c>
       <c r="B20" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>1382</v>
@@ -9153,7 +9150,7 @@
         <v>886</v>
       </c>
       <c r="B21" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>1388</v>
@@ -9179,7 +9176,7 @@
         <v>887</v>
       </c>
       <c r="B22" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>888</v>
@@ -9205,7 +9202,7 @@
         <v>889</v>
       </c>
       <c r="B23" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>890</v>
@@ -9231,7 +9228,7 @@
         <v>891</v>
       </c>
       <c r="B24" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>1391</v>
@@ -9260,13 +9257,13 @@
         <v>892</v>
       </c>
       <c r="B25" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>1395</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>77</v>
@@ -9289,7 +9286,7 @@
         <v>893</v>
       </c>
       <c r="B26" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>1400</v>
@@ -9309,7 +9306,7 @@
         <v>894</v>
       </c>
       <c r="B27" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>1403</v>
@@ -9329,7 +9326,7 @@
         <v>895</v>
       </c>
       <c r="B28" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>1404</v>
@@ -9355,7 +9352,7 @@
         <v>896</v>
       </c>
       <c r="B29" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>1409</v>
@@ -9381,7 +9378,7 @@
         <v>897</v>
       </c>
       <c r="B30" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>1414</v>
@@ -9424,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
@@ -10624,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
@@ -11377,7 +11374,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
@@ -13879,18 +13876,18 @@
         <v>642</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1620</v>
+        <v>643</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C17" s="48" t="s">
         <v>621</v>
@@ -13901,27 +13898,27 @@
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D19" s="48" t="s">
         <v>126</v>
@@ -13929,16 +13926,16 @@
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>618</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
@@ -13946,38 +13943,38 @@
         <v>639</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>370</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D23" s="48" t="s">
         <v>541</v>
@@ -13985,55 +13982,55 @@
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>522</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B26" s="48" t="s">
         <v>621</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="60" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D27" s="48" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
@@ -14041,7 +14038,7 @@
         <v>496</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D28" s="48" t="s">
         <v>521</v>
@@ -14049,24 +14046,24 @@
     </row>
     <row r="29" spans="1:4" ht="45" customHeight="1">
       <c r="B29" s="48" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D29" s="48" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="B30" s="48" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C30" s="48" t="s">
         <v>428</v>
       </c>
       <c r="D30" s="48" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
@@ -14074,15 +14071,15 @@
         <v>633</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D31" s="48" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -14120,10 +14117,10 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="49" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C1" s="49" t="s">
         <v>3</v>
@@ -14135,7 +14132,7 @@
         <v>18</v>
       </c>
       <c r="F1" s="49" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G1" s="49" t="s">
         <v>77</v>
@@ -14143,911 +14140,911 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D8" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B9" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C9" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D9" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C10" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D10" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B11" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C11" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D11" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B12" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D12" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B13" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C13" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B14" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C14" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D14" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B15" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C15" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D15" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E15" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B16" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C16" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D16" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F16" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B17" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C17" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C18" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D18" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B19" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D19" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B20" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C20" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D20" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B21" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C21" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D21" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B22" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C22" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D22" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E22" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B23" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C23" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D23" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B24" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C24" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D24" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B25" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C25" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D25" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E25" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F25" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G25" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D26" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E26" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G26" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B27" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C27" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D27" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B28" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C28" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D28" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B29" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C29" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D29" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B30" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C30" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D30" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B31" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C31" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D31" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F31" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G31" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B32" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C32" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D32" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B33" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C33" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D33" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C34" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D34" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B35" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C35" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D35" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B36" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C36" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D36" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B37" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C37" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D37" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B38" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C38" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D38" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B39" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C39" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D39" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G39" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B40" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C40" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D40" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B41" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C41" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D41" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B42" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C42" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D42" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B43" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C43" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D43" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B44" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C44" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D44" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B45" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C45" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D45" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B46" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C46" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D46" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B47" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C47" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D47" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B48" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C48" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D48" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E48" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F48" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G48" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B49" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C49" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D49" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E49" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F49" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B50" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C50" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D50" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B51" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C51" t="s">
         <v>422</v>
       </c>
       <c r="D51" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B52" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C52" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D52" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B53" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C53" t="s">
         <v>413</v>
       </c>
       <c r="D53" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B54" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C54" t="s">
         <v>423</v>
       </c>
       <c r="D54" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B55" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C55" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D55" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B56" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C56" t="s">
         <v>419</v>
       </c>
       <c r="D56" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B57" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C57" t="s">
         <v>424</v>
       </c>
       <c r="D57" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B58" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C58" t="s">
         <v>415</v>
       </c>
       <c r="D58" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B59" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C59" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D59" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B60" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C60" t="s">
         <v>421</v>
       </c>
       <c r="D60" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G60" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B61" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C61" t="s">
         <v>416</v>
@@ -15055,713 +15052,713 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B62" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C62" t="s">
         <v>553</v>
       </c>
       <c r="D62" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
+        <v>811</v>
+      </c>
+      <c r="B63" t="s">
         <v>810</v>
-      </c>
-      <c r="B63" t="s">
-        <v>809</v>
       </c>
       <c r="C63" t="s">
         <v>558</v>
       </c>
       <c r="D63" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B64" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C64" t="s">
         <v>563</v>
       </c>
       <c r="D64" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B65" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C65" t="s">
         <v>568</v>
       </c>
       <c r="D65" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B66" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C66" t="s">
         <v>573</v>
       </c>
       <c r="D66" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G66" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B67" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C67" t="s">
         <v>578</v>
       </c>
       <c r="D67" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B68" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C68" t="s">
         <v>554</v>
       </c>
       <c r="D68" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B69" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C69" t="s">
         <v>559</v>
       </c>
       <c r="D69" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B70" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C70" t="s">
         <v>564</v>
       </c>
       <c r="D70" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B71" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C71" t="s">
         <v>569</v>
       </c>
       <c r="D71" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F71" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B72" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C72" t="s">
         <v>574</v>
       </c>
       <c r="D72" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B73" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C73" t="s">
         <v>579</v>
       </c>
       <c r="D73" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B74" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C74" t="s">
         <v>555</v>
       </c>
       <c r="D74" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B75" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C75" t="s">
         <v>560</v>
       </c>
       <c r="D75" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B76" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C76" t="s">
         <v>580</v>
       </c>
       <c r="D76" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B77" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C77" t="s">
         <v>570</v>
       </c>
       <c r="D77" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F77" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G77" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B78" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C78" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D78" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B79" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C79" t="s">
         <v>577</v>
       </c>
       <c r="D79" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B80" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C80" t="s">
         <v>565</v>
       </c>
       <c r="D80" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B81" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C81" t="s">
         <v>575</v>
       </c>
       <c r="D81" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B82" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C82" t="s">
         <v>567</v>
       </c>
       <c r="D82" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B83" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C83" t="s">
         <v>556</v>
       </c>
       <c r="D83" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F83" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G83" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B84" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C84" t="s">
         <v>561</v>
       </c>
       <c r="D84" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B85" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C85" t="s">
         <v>566</v>
       </c>
       <c r="D85" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F85" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B86" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C86" t="s">
         <v>571</v>
       </c>
       <c r="D86" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B87" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C87" t="s">
         <v>576</v>
       </c>
       <c r="D87" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B88" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C88" t="s">
         <v>557</v>
       </c>
       <c r="D88" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B89" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C89" t="s">
         <v>562</v>
       </c>
       <c r="D89" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E89" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G89" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B90" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C90" t="s">
         <v>456</v>
       </c>
       <c r="D90" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
+        <v>841</v>
+      </c>
+      <c r="B91" t="s">
         <v>840</v>
-      </c>
-      <c r="B91" t="s">
-        <v>839</v>
       </c>
       <c r="C91" t="s">
         <v>461</v>
       </c>
       <c r="D91" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B92" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C92" t="s">
         <v>466</v>
       </c>
       <c r="D92" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B93" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C93" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D93" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B94" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C94" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D94" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B95" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C95" t="s">
         <v>462</v>
       </c>
       <c r="D95" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B96" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C96" t="s">
         <v>467</v>
       </c>
       <c r="D96" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B97" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C97" t="s">
         <v>472</v>
       </c>
       <c r="D97" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E97" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B98" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C98" t="s">
         <v>458</v>
       </c>
       <c r="D98" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E98" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F98" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G98" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B99" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C99" t="s">
         <v>463</v>
       </c>
       <c r="D99" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B100" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C100" t="s">
         <v>468</v>
       </c>
       <c r="D100" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B101" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C101" t="s">
         <v>473</v>
       </c>
       <c r="D101" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B102" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C102" t="s">
         <v>459</v>
       </c>
       <c r="D102" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B103" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C103" t="s">
         <v>464</v>
       </c>
       <c r="D103" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B104" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C104" t="s">
         <v>469</v>
       </c>
       <c r="D104" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B105" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C105" t="s">
         <v>474</v>
       </c>
       <c r="D105" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B106" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C106" t="s">
         <v>460</v>
       </c>
       <c r="D106" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B107" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C107" t="s">
         <v>465</v>
       </c>
       <c r="D107" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B108" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C108" t="s">
         <v>470</v>
       </c>
       <c r="D108" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B109" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C109" t="s">
         <v>475</v>
       </c>
       <c r="D109" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -15772,13 +15769,13 @@
         <v>15</v>
       </c>
       <c r="C110" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D110" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E110" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -15789,10 +15786,10 @@
         <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D111" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -15806,7 +15803,7 @@
         <v>32</v>
       </c>
       <c r="D112" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -15820,7 +15817,7 @@
         <v>483</v>
       </c>
       <c r="D113" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -15831,10 +15828,10 @@
         <v>15</v>
       </c>
       <c r="C114" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D114" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -15848,7 +15845,7 @@
         <v>42</v>
       </c>
       <c r="D115" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -15862,16 +15859,16 @@
         <v>478</v>
       </c>
       <c r="D116" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E116" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F116" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G116" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -15885,7 +15882,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -15896,10 +15893,10 @@
         <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D118" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -15913,7 +15910,7 @@
         <v>59</v>
       </c>
       <c r="D119" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -15927,7 +15924,7 @@
         <v>65</v>
       </c>
       <c r="D120" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -15941,7 +15938,7 @@
         <v>479</v>
       </c>
       <c r="D121" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -15955,10 +15952,10 @@
         <v>481</v>
       </c>
       <c r="D122" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G122" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -15972,7 +15969,7 @@
         <v>484</v>
       </c>
       <c r="D123" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -15986,10 +15983,10 @@
         <v>477</v>
       </c>
       <c r="D124" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G124" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -16003,7 +16000,7 @@
         <v>480</v>
       </c>
       <c r="D125" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -16017,7 +16014,7 @@
         <v>482</v>
       </c>
       <c r="D126" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -16031,10 +16028,10 @@
         <v>485</v>
       </c>
       <c r="D127" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G127" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -16048,7 +16045,7 @@
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -16062,7 +16059,7 @@
         <v>120</v>
       </c>
       <c r="D129" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -16076,10 +16073,10 @@
         <v>126</v>
       </c>
       <c r="D130" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G130" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -16093,190 +16090,190 @@
         <v>132</v>
       </c>
       <c r="D131" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B132" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C132" t="s">
         <v>426</v>
       </c>
       <c r="D132" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F132" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G132" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
+        <v>868</v>
+      </c>
+      <c r="B133" t="s">
         <v>867</v>
-      </c>
-      <c r="B133" t="s">
-        <v>866</v>
       </c>
       <c r="C133" t="s">
         <v>431</v>
       </c>
       <c r="D133" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B134" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C134" t="s">
         <v>436</v>
       </c>
       <c r="D134" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B135" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C135" t="s">
         <v>441</v>
       </c>
       <c r="D135" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E135" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B136" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C136" t="s">
         <v>446</v>
       </c>
       <c r="D136" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E136" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B137" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C137" t="s">
         <v>451</v>
       </c>
       <c r="D137" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B138" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C138" t="s">
         <v>427</v>
       </c>
       <c r="D138" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B139" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C139" t="s">
         <v>432</v>
       </c>
       <c r="D139" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B140" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C140" t="s">
         <v>437</v>
       </c>
       <c r="D140" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B141" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C141" t="s">
         <v>442</v>
       </c>
       <c r="D141" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B142" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C142" t="s">
         <v>447</v>
       </c>
       <c r="D142" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F142" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B143" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C143" t="s">
-        <v>878</v>
+        <v>452</v>
       </c>
       <c r="D143" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -16284,16 +16281,16 @@
         <v>879</v>
       </c>
       <c r="B144" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C144" t="s">
         <v>428</v>
       </c>
       <c r="D144" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F144" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -16301,13 +16298,13 @@
         <v>880</v>
       </c>
       <c r="B145" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C145" t="s">
         <v>433</v>
       </c>
       <c r="D145" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -16315,13 +16312,13 @@
         <v>881</v>
       </c>
       <c r="B146" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C146" t="s">
         <v>450</v>
       </c>
       <c r="D146" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -16329,13 +16326,13 @@
         <v>882</v>
       </c>
       <c r="B147" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C147" t="s">
         <v>449</v>
       </c>
       <c r="D147" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -16343,13 +16340,13 @@
         <v>883</v>
       </c>
       <c r="B148" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C148" t="s">
         <v>435</v>
       </c>
       <c r="D148" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -16357,19 +16354,19 @@
         <v>884</v>
       </c>
       <c r="B149" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C149" t="s">
         <v>454</v>
       </c>
       <c r="D149" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F149" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G149" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -16377,13 +16374,13 @@
         <v>885</v>
       </c>
       <c r="B150" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C150" t="s">
         <v>438</v>
       </c>
       <c r="D150" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -16391,13 +16388,13 @@
         <v>886</v>
       </c>
       <c r="B151" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C151" t="s">
         <v>430</v>
       </c>
       <c r="D151" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -16405,13 +16402,13 @@
         <v>887</v>
       </c>
       <c r="B152" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C152" t="s">
         <v>888</v>
       </c>
       <c r="D152" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -16419,13 +16416,13 @@
         <v>889</v>
       </c>
       <c r="B153" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C153" t="s">
         <v>890</v>
       </c>
       <c r="D153" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -16433,13 +16430,13 @@
         <v>891</v>
       </c>
       <c r="B154" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C154" t="s">
         <v>443</v>
       </c>
       <c r="D154" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -16447,22 +16444,22 @@
         <v>892</v>
       </c>
       <c r="B155" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C155" t="s">
         <v>448</v>
       </c>
       <c r="D155" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E155" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F155" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G155" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -16470,13 +16467,13 @@
         <v>893</v>
       </c>
       <c r="B156" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C156" t="s">
         <v>453</v>
       </c>
       <c r="D156" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -16484,13 +16481,13 @@
         <v>894</v>
       </c>
       <c r="B157" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C157" t="s">
         <v>429</v>
       </c>
       <c r="D157" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -16498,13 +16495,13 @@
         <v>895</v>
       </c>
       <c r="B158" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C158" t="s">
         <v>434</v>
       </c>
       <c r="D158" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -16512,13 +16509,13 @@
         <v>896</v>
       </c>
       <c r="B159" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C159" t="s">
         <v>439</v>
       </c>
       <c r="D159" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -16526,13 +16523,13 @@
         <v>897</v>
       </c>
       <c r="B160" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C160" t="s">
         <v>444</v>
       </c>
       <c r="D160" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -16546,10 +16543,10 @@
         <v>487</v>
       </c>
       <c r="D161" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E161" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -16563,7 +16560,7 @@
         <v>492</v>
       </c>
       <c r="D162" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -16577,7 +16574,7 @@
         <v>497</v>
       </c>
       <c r="D163" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -16591,7 +16588,7 @@
         <v>502</v>
       </c>
       <c r="D164" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -16605,7 +16602,7 @@
         <v>507</v>
       </c>
       <c r="D165" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -16619,7 +16616,7 @@
         <v>512</v>
       </c>
       <c r="D166" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -16633,7 +16630,7 @@
         <v>517</v>
       </c>
       <c r="D167" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -16647,7 +16644,7 @@
         <v>907</v>
       </c>
       <c r="D168" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -16661,10 +16658,10 @@
         <v>909</v>
       </c>
       <c r="D169" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E169" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -16678,7 +16675,7 @@
         <v>488</v>
       </c>
       <c r="D170" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -16692,7 +16689,7 @@
         <v>493</v>
       </c>
       <c r="D171" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -16706,7 +16703,7 @@
         <v>498</v>
       </c>
       <c r="D172" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -16720,7 +16717,7 @@
         <v>503</v>
       </c>
       <c r="D173" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -16734,7 +16731,7 @@
         <v>508</v>
       </c>
       <c r="D174" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -16748,7 +16745,7 @@
         <v>513</v>
       </c>
       <c r="D175" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -16762,7 +16759,7 @@
         <v>917</v>
       </c>
       <c r="D176" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -16776,7 +16773,7 @@
         <v>523</v>
       </c>
       <c r="D177" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -16790,7 +16787,7 @@
         <v>920</v>
       </c>
       <c r="D178" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -16804,7 +16801,7 @@
         <v>489</v>
       </c>
       <c r="D179" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -16818,7 +16815,7 @@
         <v>494</v>
       </c>
       <c r="D180" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -16832,7 +16829,7 @@
         <v>924</v>
       </c>
       <c r="D181" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -16846,7 +16843,7 @@
         <v>926</v>
       </c>
       <c r="D182" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -16860,7 +16857,7 @@
         <v>509</v>
       </c>
       <c r="D183" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -16874,7 +16871,7 @@
         <v>514</v>
       </c>
       <c r="D184" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -16888,10 +16885,10 @@
         <v>519</v>
       </c>
       <c r="D185" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E185" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -16905,7 +16902,7 @@
         <v>931</v>
       </c>
       <c r="D186" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -16919,7 +16916,7 @@
         <v>529</v>
       </c>
       <c r="D187" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -16933,7 +16930,7 @@
         <v>490</v>
       </c>
       <c r="D188" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -16947,7 +16944,7 @@
         <v>495</v>
       </c>
       <c r="D189" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -16961,7 +16958,7 @@
         <v>500</v>
       </c>
       <c r="D190" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -16975,7 +16972,7 @@
         <v>505</v>
       </c>
       <c r="D191" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -16989,7 +16986,7 @@
         <v>510</v>
       </c>
       <c r="D192" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -17003,7 +17000,7 @@
         <v>515</v>
       </c>
       <c r="D193" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -17017,7 +17014,7 @@
         <v>520</v>
       </c>
       <c r="D194" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -17031,7 +17028,7 @@
         <v>525</v>
       </c>
       <c r="D195" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -17045,7 +17042,7 @@
         <v>530</v>
       </c>
       <c r="D196" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -17059,7 +17056,7 @@
         <v>491</v>
       </c>
       <c r="D197" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -17073,10 +17070,10 @@
         <v>496</v>
       </c>
       <c r="D198" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E198" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -17090,7 +17087,7 @@
         <v>501</v>
       </c>
       <c r="D199" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -17104,7 +17101,7 @@
         <v>506</v>
       </c>
       <c r="D200" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -17118,7 +17115,7 @@
         <v>511</v>
       </c>
       <c r="D201" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -17132,7 +17129,7 @@
         <v>516</v>
       </c>
       <c r="D202" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -17146,10 +17143,10 @@
         <v>521</v>
       </c>
       <c r="D203" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G203" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -17163,10 +17160,10 @@
         <v>526</v>
       </c>
       <c r="D204" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G204" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -17180,7 +17177,7 @@
         <v>532</v>
       </c>
       <c r="D205" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -17194,7 +17191,7 @@
         <v>953</v>
       </c>
       <c r="D206" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -17208,7 +17205,7 @@
         <v>542</v>
       </c>
       <c r="D207" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -17222,7 +17219,7 @@
         <v>547</v>
       </c>
       <c r="D208" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -17236,7 +17233,7 @@
         <v>533</v>
       </c>
       <c r="D209" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -17250,7 +17247,7 @@
         <v>538</v>
       </c>
       <c r="D210" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -17264,7 +17261,7 @@
         <v>543</v>
       </c>
       <c r="D211" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -17278,7 +17275,7 @@
         <v>548</v>
       </c>
       <c r="D212" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -17292,7 +17289,7 @@
         <v>534</v>
       </c>
       <c r="D213" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -17306,13 +17303,13 @@
         <v>539</v>
       </c>
       <c r="D214" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E214" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F214" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -17326,7 +17323,7 @@
         <v>544</v>
       </c>
       <c r="D215" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -17340,13 +17337,13 @@
         <v>549</v>
       </c>
       <c r="D216" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F216" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G216" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -17360,10 +17357,10 @@
         <v>535</v>
       </c>
       <c r="D217" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G217" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -17377,7 +17374,7 @@
         <v>540</v>
       </c>
       <c r="D218" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -17391,7 +17388,7 @@
         <v>545</v>
       </c>
       <c r="D219" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -17405,10 +17402,10 @@
         <v>550</v>
       </c>
       <c r="D220" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G220" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -17422,7 +17419,7 @@
         <v>536</v>
       </c>
       <c r="D221" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -17436,7 +17433,7 @@
         <v>970</v>
       </c>
       <c r="D222" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -17450,7 +17447,7 @@
         <v>546</v>
       </c>
       <c r="D223" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -17464,7 +17461,7 @@
         <v>551</v>
       </c>
       <c r="D224" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -17478,7 +17475,7 @@
         <v>582</v>
       </c>
       <c r="D225" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -17492,13 +17489,13 @@
         <v>587</v>
       </c>
       <c r="D226" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E226" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F226" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -17512,7 +17509,7 @@
         <v>592</v>
       </c>
       <c r="D227" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -17526,13 +17523,13 @@
         <v>597</v>
       </c>
       <c r="D228" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E228" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F228" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -17546,7 +17543,7 @@
         <v>583</v>
       </c>
       <c r="D229" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -17560,13 +17557,13 @@
         <v>596</v>
       </c>
       <c r="D230" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E230" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F230" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -17580,13 +17577,13 @@
         <v>588</v>
       </c>
       <c r="D231" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E231" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F231" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -17600,7 +17597,7 @@
         <v>598</v>
       </c>
       <c r="D232" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -17614,7 +17611,7 @@
         <v>584</v>
       </c>
       <c r="D233" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -17628,10 +17625,10 @@
         <v>589</v>
       </c>
       <c r="D234" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E234" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -17645,7 +17642,7 @@
         <v>594</v>
       </c>
       <c r="D235" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -17659,7 +17656,7 @@
         <v>585</v>
       </c>
       <c r="D236" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -17673,7 +17670,7 @@
         <v>987</v>
       </c>
       <c r="D237" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -17687,10 +17684,10 @@
         <v>595</v>
       </c>
       <c r="D238" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E238" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -17704,7 +17701,7 @@
         <v>586</v>
       </c>
       <c r="D239" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -17718,7 +17715,7 @@
         <v>591</v>
       </c>
       <c r="D240" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -17732,13 +17729,13 @@
         <v>593</v>
       </c>
       <c r="D241" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E241" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F241" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -17780,7 +17777,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
@@ -17824,13 +17821,13 @@
     </row>
     <row r="2" spans="1:17" ht="45" customHeight="1">
       <c r="A2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>363</v>
@@ -17864,13 +17861,13 @@
     </row>
     <row r="3" spans="1:17" ht="30" customHeight="1">
       <c r="A3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>375</v>
@@ -17900,13 +17897,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>379</v>
@@ -17922,13 +17919,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>366</v>
@@ -17959,10 +17956,10 @@
     </row>
     <row r="6" spans="1:17" ht="60" customHeight="1">
       <c r="A6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>1013</v>
@@ -17983,13 +17980,13 @@
     </row>
     <row r="7" spans="1:17" ht="75" customHeight="1">
       <c r="A7" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>368</v>
@@ -18029,13 +18026,13 @@
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1">
       <c r="A8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>378</v>
@@ -18074,13 +18071,13 @@
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1">
       <c r="A9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B9" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>365</v>
@@ -18108,19 +18105,19 @@
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="21" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>371</v>
@@ -18151,13 +18148,13 @@
     </row>
     <row r="11" spans="1:17" ht="30" customHeight="1">
       <c r="A11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B11" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>376</v>
@@ -18175,13 +18172,13 @@
     </row>
     <row r="12" spans="1:17" ht="30" customHeight="1">
       <c r="A12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B12" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>367</v>
@@ -18211,13 +18208,13 @@
     </row>
     <row r="13" spans="1:17" ht="30" customHeight="1">
       <c r="A13" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B13" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>373</v>
@@ -18248,13 +18245,13 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B14" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>364</v>
@@ -18284,13 +18281,13 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B15" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>370</v>
@@ -18320,13 +18317,13 @@
     </row>
     <row r="16" spans="1:17" ht="30" customHeight="1">
       <c r="A16" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B16" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>381</v>
@@ -18350,13 +18347,13 @@
     </row>
     <row r="17" spans="1:17" ht="30" customHeight="1">
       <c r="A17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B17" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>372</v>
@@ -18386,13 +18383,13 @@
     </row>
     <row r="18" spans="1:17" ht="30" customHeight="1">
       <c r="A18" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>374</v>
@@ -18420,10 +18417,10 @@
     </row>
     <row r="19" spans="1:17" ht="30" customHeight="1">
       <c r="A19" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B19" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>1064</v>
@@ -18454,10 +18451,10 @@
     </row>
     <row r="20" spans="1:17" ht="30" customHeight="1">
       <c r="A20" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B20" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>1069</v>
@@ -18594,13 +18591,13 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="33" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>384</v>
@@ -18635,13 +18632,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="33" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D3" s="36" t="s">
         <v>388</v>
@@ -18666,13 +18663,13 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="33" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>393</v>
@@ -18707,13 +18704,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="33" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>394</v>
@@ -18743,13 +18740,13 @@
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1">
       <c r="A6" s="33" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>398</v>
@@ -18786,13 +18783,13 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="33" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>399</v>
@@ -18817,13 +18814,13 @@
     </row>
     <row r="8" spans="1:18" ht="45" customHeight="1">
       <c r="A8" s="33" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>403</v>
@@ -18858,13 +18855,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="33" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>404</v>
@@ -18901,13 +18898,13 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="33" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>408</v>
@@ -18942,13 +18939,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="33" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D11" s="36" t="s">
         <v>409</v>
@@ -18973,13 +18970,13 @@
     </row>
     <row r="12" spans="1:18" ht="45" customHeight="1">
       <c r="A12" s="33" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>383</v>
@@ -19018,10 +19015,10 @@
     </row>
     <row r="13" spans="1:18" ht="30" customHeight="1">
       <c r="A13" s="33" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>1126</v>
@@ -19059,13 +19056,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="33" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>386</v>
@@ -19096,13 +19093,13 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="33" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>387</v>
@@ -19133,10 +19130,10 @@
     </row>
     <row r="16" spans="1:18" ht="30" customHeight="1">
       <c r="A16" s="33" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>1136</v>
@@ -19168,13 +19165,13 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="33" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>390</v>
@@ -19209,13 +19206,13 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="33" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>391</v>
@@ -19244,13 +19241,13 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="33" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>392</v>
@@ -19281,13 +19278,13 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="33" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>395</v>
@@ -19324,10 +19321,10 @@
     </row>
     <row r="21" spans="1:17" ht="30" customHeight="1">
       <c r="A21" s="33" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>1151</v>
@@ -19369,13 +19366,13 @@
     </row>
     <row r="22" spans="1:17" ht="45" customHeight="1">
       <c r="A22" s="33" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>397</v>
@@ -19408,13 +19405,13 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="33" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>400</v>
@@ -19443,13 +19440,13 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="33" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D24" s="18" t="s">
         <v>401</v>
@@ -19488,13 +19485,13 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="33" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>402</v>
@@ -19523,13 +19520,13 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="33" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>405</v>
@@ -19562,13 +19559,13 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="33" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>406</v>
@@ -19597,13 +19594,13 @@
     </row>
     <row r="28" spans="1:17" ht="60" customHeight="1">
       <c r="A28" s="33" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>407</v>
@@ -19634,10 +19631,10 @@
     </row>
     <row r="29" spans="1:17" ht="30" customHeight="1">
       <c r="A29" s="33" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>1180</v>
@@ -19734,10 +19731,10 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1184</v>
@@ -19751,10 +19748,10 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>1185</v>
@@ -19768,10 +19765,10 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>1186</v>
@@ -19785,10 +19782,10 @@
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1">
       <c r="A5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B5" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>1188</v>
@@ -19808,10 +19805,10 @@
     </row>
     <row r="6" spans="1:15" ht="60" customHeight="1">
       <c r="A6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>1191</v>
@@ -19831,10 +19828,10 @@
     </row>
     <row r="7" spans="1:15" ht="30" customHeight="1">
       <c r="A7" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>1195</v>
@@ -19851,10 +19848,10 @@
     </row>
     <row r="8" spans="1:15" ht="45" customHeight="1">
       <c r="A8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B8" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>1198</v>
@@ -19874,10 +19871,10 @@
     </row>
     <row r="9" spans="1:15" ht="45" customHeight="1">
       <c r="A9" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>1201</v>
@@ -19894,10 +19891,10 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B10" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>1204</v>
@@ -19914,10 +19911,10 @@
     </row>
     <row r="11" spans="1:15" ht="60" customHeight="1">
       <c r="A11" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>1207</v>
@@ -19940,10 +19937,10 @@
     </row>
     <row r="12" spans="1:15" ht="30" customHeight="1">
       <c r="A12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B12" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>1212</v>
@@ -19963,10 +19960,10 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B13" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>1214</v>
@@ -19980,10 +19977,10 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B14" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>1215</v>
